--- a/research/dataset/TruthLens_Dataset.xlsx
+++ b/research/dataset/TruthLens_Dataset.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07T15:17:01+00:00</t>
+          <t>2026-09-07T15:38:20+00:00</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a4b03af</t>
+          <t>9ab9768</t>
         </is>
       </c>
     </row>
@@ -688,14 +688,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK27"/>
+  <dimension ref="A1:AK35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -3673,6 +3673,870 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>item-0027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0196</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/4194321227564873</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/west-asia-conflict-old-video-falsely-viral-as-footage-from-tel-aviv-after-iranian-strike/</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Israel occupied schools and hospitals, killing 160 Iranian school girls</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/west-asia-conflict-old-video-falsely-viral-as-footage-from-tel-aviv-after-iranian-strike/</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>3a03a21e6b7074a92d5b7fb12a2a833e76c4f2a5f65cf4d272428b2310b98250</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>2026-09-07T13:51:43.696587+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>item-0028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0316</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://twitter.com/pathan_sumaya/status/2015708362789556721</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-from-bangladesh-of-man-popping-childs-balloons-falsely-shared-with-communal-angle/</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>A person who is doing brutality against a Muslim balloon seller or a crowd instead of helping takes a video?</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-from-bangladesh-of-man-popping-childs-balloons-falsely-shared-with-communal-angle/</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="W29" t="b">
+        <v>1</v>
+      </c>
+      <c r="X29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ce0e74bf0e7f76bf93acfd65bd4ba62b751ff8a7e151d304ca05a7bc178c4da3</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:08:54.320547+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>item-0029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0382</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://twitter.com/yoursurajnaik/status/1997721155235713176</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/old-video-of-aviation-minister-k-r-naidu-dancing-falsely-viral-amid-indigo-crisis/</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>This government has mastered one thing: entertainment over governance.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/old-video-of-aviation-minister-k-r-naidu-dancing-falsely-viral-amid-indigo-crisis/</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>127ecea126d89ac271dab414e69d52e400ae5876abe319897479152099993014</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:15:35.466818+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>item-0030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0407</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://twitter.com/rvaidya2000/status/1995691015437713467</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-udhayanidhi-stalin-using-computer-without-switching-it-on-is-ai-generated/</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>He's so brilliant that he can work on a computer even without switching it on!</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-udhayanidhi-stalin-using-computer-without-switching-it-on-is-ai-generated/</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W31" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>37b3dc508f0e042df4bb597d4596bfb17c69cac6a7a290fe533a456b175974d9</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:19:08.313987+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>item-0031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0522</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://twitter.com/MrSinha_/status/1983456538309317021</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/no-rahul-gandhi-did-not-call-chhath-puja-a-drama-claim-by-modi-bjp-camp-false/</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi called Chhath Puja 'drama'</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/no-rahul-gandhi-did-not-call-chhath-puja-a-drama-claim-by-modi-bjp-camp-false/</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="W32" t="b">
+        <v>1</v>
+      </c>
+      <c r="X32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD32" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>964b903e31486376a95b3a9b7b182d72568a50e195ee17dd24960fa3b4cc9c2f</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:32:00.027400+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>item-0032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0567</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>https://twitter.com/JaipurDialogues/status/1980688390107590811</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/delhi-pollution-old-video-shared-to-claim-stubble-burning-in-punjab-is-to-be-blamed-not-diwali-crackers/</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Liberals are blaming Diwali and fire crackers for air pollution.</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/delhi-pollution-old-video-shared-to-claim-stubble-burning-in-punjab-is-to-be-blamed-not-diwali-crackers/</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="W33" t="b">
+        <v>0</v>
+      </c>
+      <c r="X33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD33" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>6b3c402e397a12bad8a3cbbe7d7ab1c9d144b94f6724e18b87ca583f6782e990</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:36:53.597286+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>item-0033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0568</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://twitter.com/MrTiwaria/status/1980725821288632349</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/delhi-pollution-old-video-shared-to-claim-stubble-burning-in-punjab-is-to-be-blamed-not-diwali-crackers/</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>उदारवादी लिब्रांडु लोग वायु प्रदूषण के लिए दिवाली और पटाखों को ज़िम्मेदार ठहराएँगे।</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/delhi-pollution-old-video-shared-to-claim-stubble-burning-in-punjab-is-to-be-blamed-not-diwali-crackers/</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="W34" t="b">
+        <v>0</v>
+      </c>
+      <c r="X34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD34" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>6b3c402e397a12bad8a3cbbe7d7ab1c9d144b94f6724e18b87ca583f6782e990</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:36:53.599393+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>item-0034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0021</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://twitter.com/foxwoundband/status/1266613385862447104</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-atlanta-did-not-deploy-a-child-militia-during-protests.html</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Atlanta has deployed a child militia at Lenox Mall fitted with riot shields and batons.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-atlanta-did-not-deploy-a-child-militia-during-protests.html</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="b">
+        <v>1</v>
+      </c>
+      <c r="X35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>4b48a848c5f05592dadb58da56db7e9f10ff3752cbef3e5d9b806519bb69c622</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:37:22.560671+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3684,7 +4548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P57"/>
+  <dimension ref="A1:P65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6163,6 +7027,222 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>item-0027</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Israel occupied schools and hospitals, killing 160 Iranian school girls</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>item-0028</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>A person who is doing brutality against a Muslim balloon seller or a crowd instead of helping takes a video?</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>item-0029</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>This government has mastered one thing: entertainment over governance.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>item-0030</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>He's so brilliant that he can work on a computer even without switching it on!</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>item-0031</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi called Chhath Puja 'drama'</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>item-0032</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Liberals are blaming Diwali and fire crackers for air pollution.</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>item-0033</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>उदारवादी लिब्रांडु लोग वायु प्रदूषण के लिए दिवाली और पटाखों को ज़िम्मेदार ठहराएँगे।</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>item-0034</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Atlanta has deployed a child militia at Lenox Mall fitted with riot shields and batons.</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6174,7 +7254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7120,6 +8200,11 @@
           <t>cand-ap-altnews-0196</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>item-0027</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -7185,6 +8270,11 @@
           <t>cand-ap-altnews-0316</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>item-0028</t>
+        </is>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -7250,6 +8340,11 @@
           <t>cand-ap-altnews-0382</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>item-0029</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -7315,6 +8410,11 @@
           <t>cand-ap-altnews-0407</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>item-0030</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -7380,6 +8480,11 @@
           <t>cand-ap-altnews-0522</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>item-0031</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -7445,6 +8550,11 @@
           <t>cand-ap-altnews-0567</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>item-0032</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -7510,6 +8620,11 @@
           <t>cand-ap-altnews-0568</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>item-0033</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -7703,6 +8818,11 @@
       <c r="A24" t="inlineStr">
         <is>
           <t>cand-ap-leadstories-0021</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>item-0034</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7834,7 +8954,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0112</t>
+          <t>cand-ap-leadstories-0212</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7854,12 +8974,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=2klmuggOElE</t>
+          <t>https://www.youtube.com/watch?v=J0CLMqpsrgY</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-22-point-meme-is-mix-of-false-truth-opinion.html</t>
+          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-doctors-do-recommend-vitamins-and-sunlight-for-peoples-health.html</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7869,7 +8989,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-07T14:51:51.927886+00:00</t>
+          <t>2026-09-07T15:05:48.862967+00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -7878,7 +8998,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -7887,19 +9007,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>The Queen has promised the nation that better days are ahead, during a special address on Sunday.</t>
+          <t>'almost no evidence' is a misrepresentation of Dr Belchetz statement that 'there are many studies showing benefits to taking vitamins and supplements', according to the CBC article.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+          <t>llama3.2 (conf=0.90): The original claim made in this post's caption states that 'almost no evidence backs up claims from vitamin and supplement industry'. However, according to Dr Belchetz' statement cited on YouTube (referenced by the same source as CBC article), there are many studies showing benefits of taking vitamins. The use of the term "almost" is misleading because it implies a lack of any evidence when in fact multiple researches support its claims.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0149</t>
+          <t>cand-ap-leadstories-0223</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7914,17 +9034,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>facebook</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/watch/?v=251364862815976</t>
+          <t>https://www.youtube.com/watch?v=ad1ysX2iLmA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-brooklyn-subway-attack-not-related-to-black-lives-matter-protests.html</t>
+          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-birth-certificate-does-not-prove-donald-trump-had-son-with-ghislaine-maxwell.html</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7934,7 +9054,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-07T14:58:31.251937+00:00</t>
+          <t>2026-09-07T15:08:10.465015+00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -7952,19 +9072,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>#BlackLivesMatter attacking innocent white woman.</t>
+          <t>The @realJimmyTrump account has recently changed its photo from a picture of Kieran Culkin to the Birth Certificate and a meme image known as "Zuckertrump." The identity of Rogue WH Snr Advisor remains unknown, but they are most certainly not the son of President Trump and Ghislaine Maxwell.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The post's caption directly states that #BlackLivesMatter is 'attacking' an innocent white woman. The phrase suggests a causal relationship between BLM protests and the attack on Oct. 23, 2019. However, according to the article, there was no connection between Thompson's actions (a repeat transit offender) and Black Lives Matter.</t>
+          <t>llama3.2 (conf=1.00): The post's caption changes the image on @realJimmyTrump account from a picture of Kieran Culkin to one that includes the Birth Certificate with 'Zuckertrump' meme, which is an edited version of Donald Trump and implies he was involved in some scandalous activity (sex offender) but does not state it directly. The post's caption also says Rogue WH Snr Advisor are most certainly NOT Ghislaine Maxwell &amp; President trump son - making this claim MISINFORMATION_SOURCE.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0177</t>
+          <t>cand-ap-leadstories-0245</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7984,12 +9104,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=1YJsxMcAJoA</t>
+          <t>https://www.youtube.com/watch?v=TYfXE8QeFHE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-nbc-news-did-not-report-all-americans-will-receive-a-microchip-implant-by-the-end-of-the-year.html</t>
+          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-clark-hunt-did-not-threaten-to-fire-his-players-and-staff-if-they-dont-stand-for-the-national-anthem.html</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -7999,7 +9119,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-07T15:01:38.903001+00:00</t>
+          <t>2026-09-07T15:09:56.550526+00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -8008,28 +9128,28 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Coverage under Obamacare will require an implantable microchip?</t>
+          <t>'You are all simply paid performers on a stage and that field is my stage! You will stand, with your hand over your heart and with respect, when our Country's National Anthem is being played or you will no longer be a Kansas City Chief, a Coach for the Kansas City Chiefs or have any association with the Chiefs Organization!'</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+          <t>llama3.2 (conf=1.00): The caption of this YouTube post is identical to the claim mentioned at the beginning of the fact-check article, which was debunked as a false attribution to Clark Hunt and other NFL owners.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0184</t>
+          <t>cand-ap-leadstories-0273</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -8044,17 +9164,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://twitter.com/SteveGuest/status/1276221457467609091</t>
+          <t>https://www.youtube.com/watch?v=WvKSy1bwT70</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-biden-quotes-wrong-number-of-american-covid19-deaths-not-over-120-million.html</t>
+          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-the-cdc-does-recommend-buying-and-using-face-masks-even-if-you-are-healthy.html</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8064,7 +9184,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-07T15:04:01.666025+00:00</t>
+          <t>2026-09-07T15:17:06.077762+00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -8082,19 +9202,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>over 120 million people died in the United States from COVID-19.</t>
+          <t>Yes, this is a real flyer,</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+          <t>llama3.2 (conf=1.00): The post's caption states that President Trump announced the CDC is changing its guidelines to recommend people wear simple cloth face masks, which includes a claim about healthy individuals not needing to buy or use face masks. This matches with what was stated in an outdated Delaware Health and Social Services infographic published March 2020.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0211</t>
+          <t>cand-ap-leadstories-0314</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -8114,12 +9234,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=E94pqy2rB7g</t>
+          <t>https://www.youtube.com/watch?v=VhirLohgDRc</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-doctors-do-recommend-vitamins-and-sunlight-for-peoples-health.html</t>
+          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-no-evidence-european-royals-are-hunting-naked-children-for-fun-at-human-hunting-parties.html</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8129,7 +9249,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-07T15:05:48.860472+00:00</t>
+          <t>2026-09-07T15:25:59.766110+00:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -8145,17 +9265,26 @@
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>European royals killing naked children for fun at human hunting parties.</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The claim in the Facebook post is that 'no doctor on TV tells us to strengthen our immune system: vitamins, eat right, sunlight.' However, according to the fact-check article, this claim has been debunked as false. The CDC recommends various nutrients and spending time outdoors for overall health benefits, which contradicts the idea presented by the meme.</t>
+          <t>llama3.2 (conf=1.00): The caption of this YouTube post directly links to the same source (Kevin Annetts' blog) which originally published and promoted the debunked claim. The text itself is a direct copy from Kevin Annett's video, making no distinction between fact or fiction.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0212</t>
+          <t>cand-mass-0027</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>item-0019</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -8165,127 +9294,107 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>youtube</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=J0CLMqpsrgY</t>
+          <t>https://www.instagram.com/reel/DX7LBwesE-o/</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-doctors-do-recommend-vitamins-and-sunlight-for-peoples-health.html</t>
+          <t>https://www.altnews.in/bjp-media-outlets-share-holi-video-as-people-celebrating-bjp-victory-in-bengal/</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v2.jsonl</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-09-07T15:05:48.862967+00:00</t>
+          <t>2026-08-18T00:59:01.077843+00:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>0.9</v>
+          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>False claim: The post's own caption asserts that it depicts people celebrating a political event (BJP victory), but actually shows a pre-election celebration during Holi.</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>'almost no evidence' is a misrepresentation of Dr Belchetz statement that 'there are many studies showing benefits to taking vitamins and supplements', according to the CBC article.</t>
+          <t>Celebrations of Jai Sri Ram at the Holi celebrations in Kolkata, which took place two months before May 4th</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=0.90): The original claim made in this post's caption states that 'almost no evidence backs up claims from vitamin and supplement industry'. However, according to Dr Belchetz' statement cited on YouTube (referenced by the same source as CBC article), there are many studies showing benefits of taking vitamins. The use of the term "almost" is misleading because it implies a lack of any evidence when in fact multiple researches support its claims.</t>
+          <t>llama3.2 judge (confidence=0.90): The Instagram Post’s Own Caption Asserts the False Claim</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0223</t>
+          <t>cand-mass-0088</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ELIGIBLE</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>youtube</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ad1ysX2iLmA</t>
+          <t>https://www.instagram.com/reel/DPcCJWxga06/</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-birth-certificate-does-not-prove-donald-trump-had-son-with-ghislaine-maxwell.html</t>
+          <t>https://www.altnews.in/yogi-adityanath-left-to-hear-criticism-of-govt-while-ravi-kishan-was-enjoying-doctored-video-viral/</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v2.jsonl</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-09-07T15:08:10.465015+00:00</t>
+          <t>2026-08-18T01:51:54.674020+00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>The @realJimmyTrump account has recently changed its photo from a picture of Kieran Culkin to the Birth Certificate and a meme image known as "Zuckertrump." The identity of Rogue WH Snr Advisor remains unknown, but they are most certainly not the son of President Trump and Ghislaine Maxwell.</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>llama3.2 (conf=1.00): The post's caption changes the image on @realJimmyTrump account from a picture of Kieran Culkin to one that includes the Birth Certificate with 'Zuckertrump' meme, which is an edited version of Donald Trump and implies he was involved in some scandalous activity (sex offender) but does not state it directly. The post's caption also says Rogue WH Snr Advisor are most certainly NOT Ghislaine Maxwell &amp; President trump son - making this claim MISINFORMATION_SOURCE.</t>
+          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; REJECTED</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Judged NOT the misinformation source (confidence=1.00): </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0245</t>
+          <t>cand-thequint-0182</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>item-0021</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8295,41 +9404,33 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>youtube</t>
+          <t>thequint.com</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TYfXE8QeFHE</t>
+          <t>https://www.instagram.com/reel/DRmx_YwjN7Y/</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-clark-hunt-did-not-threaten-to-fire-his-players-and-staff-if-they-dont-stand-for-the-national-anthem.html</t>
+          <t>https://www.thequint.com/news/webqoof/ai-generated-yogi-lifting-weighting-without-his-hands-fact-check</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v2_mass_thequint.jsonl</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-09-07T15:09:56.550526+00:00</t>
+          <t>2026-08-18T05:29:58.023010+00:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; ELIGIBLE</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -8338,19 +9439,24 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>'You are all simply paid performers on a stage and that field is my stage! You will stand, with your hand over your heart and with respect, when our Country's National Anthem is being played or you will no longer be a Kansas City Chief, a Coach for the Kansas City Chiefs or have any association with the Chiefs Organization!'</t>
+          <t>INDIAN YOGI MOVES 95 Kgs of weight in the gym with his mind!</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The caption of this YouTube post is identical to the claim mentioned at the beginning of the fact-check article, which was debunked as a false attribution to Clark Hunt and other NFL owners.</t>
+          <t>llama3.2 judge (confidence=1.00): The caption text itself makes a specific false assertion about lifting '130 kgs' (not mentioned) and claims that it's done using one's 'mind', which is the exact same claim being debunked in the article.. NOT yet human/manual-reviewed.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0247</t>
+          <t>cand-vishvas-1173</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>item-0022</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8360,287 +9466,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>youtube</t>
+          <t>vishvasnews.com</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=xKPWngYf2Wk</t>
+          <t>https://www.instagram.com/reel/C3tynQjr_wI/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-doctors-claim-that-no-one-has-died-from-the-coronavirus-is-not-true.html</t>
+          <t>https://www.vishvasnews.com/politics/fact-check-akhilesh-yadav-old-video-from-kanpur-is-being-shared-as-meeting-farmers-in-delhi/</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v2_mass_vishvas.jsonl</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-09-07T15:10:29.017026+00:00</t>
+          <t>2026-08-18T10:12:40.325601+00:00</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>1</v>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; ELIGIBLE -&gt; UNRESOLVED -&gt; ELIGIBLE</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>The World Health Organization (WHO) has officially declared the outbreak of novel coronavirus disease, COVID-19, a pandemic.</t>
+          <t>अखिलेश यादव किसानों से मिलने दिल्ली पहुंचे।</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cand-mass-0027</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>item-0019</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>altnews.in</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/reel/DX7LBwesE-o/</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.altnews.in/bjp-media-outlets-share-holi-video-as-people-celebrating-bjp-victory-in-bengal/</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>candidates_v2.jsonl</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-08-18T00:59:01.077843+00:00</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>False claim: The post's own caption asserts that it depicts people celebrating a political event (BJP victory), but actually shows a pre-election celebration during Holi.</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Celebrations of Jai Sri Ram at the Holi celebrations in Kolkata, which took place two months before May 4th</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>llama3.2 judge (confidence=0.90): The Instagram Post’s Own Caption Asserts the False Claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>cand-mass-0088</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>altnews.in</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/reel/DPcCJWxga06/</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.altnews.in/yogi-adityanath-left-to-hear-criticism-of-govt-while-ravi-kishan-was-enjoying-doctored-video-viral/</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>candidates_v2.jsonl</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-08-18T01:51:54.674020+00:00</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; REJECTED</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Judged NOT the misinformation source (confidence=1.00): </t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>cand-thequint-0182</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>item-0021</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>thequint.com</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/reel/DRmx_YwjN7Y/</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.thequint.com/news/webqoof/ai-generated-yogi-lifting-weighting-without-his-hands-fact-check</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>candidates_v2_mass_thequint.jsonl</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-08-18T05:29:58.023010+00:00</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>INDIAN YOGI MOVES 95 Kgs of weight in the gym with his mind!</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>llama3.2 judge (confidence=1.00): The caption text itself makes a specific false assertion about lifting '130 kgs' (not mentioned) and claims that it's done using one's 'mind', which is the exact same claim being debunked in the article.. NOT yet human/manual-reviewed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>cand-vishvas-1173</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>item-0022</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>vishvasnews.com</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/reel/C3tynQjr_wI/</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.vishvasnews.com/politics/fact-check-akhilesh-yadav-old-video-from-kanpur-is-being-shared-as-meeting-farmers-in-delhi/</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>candidates_v2_mass_vishvas.jsonl</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-08-18T10:12:40.325601+00:00</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; ELIGIBLE -&gt; UNRESOLVED -&gt; ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>अखिलेश यादव किसानों से मिलने दिल्ली पहुंचे।</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
         <is>
           <t>llama3.2 judge (confidence=1.00): The caption text itself makes the specific false assertion that 'अखिलेश यादव' is meeting with farmers in Delhi, which contradicts the fact-check article's conclusion.. NOT yet human/manual-reviewed.</t>
         </is>
@@ -8657,7 +9521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -8684,7 +9548,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07T15:17:01+00:00</t>
+          <t>2026-09-07T15:38:20+00:00</t>
         </is>
       </c>
     </row>
@@ -8695,7 +9559,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -8715,7 +9579,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6">
@@ -8757,55 +9621,55 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    MISLEADING</t>
+          <t xml:space="preserve">    UNVERIFIED</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TRUE</t>
+          <t xml:space="preserve">    MISLEADING</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- platform distribution ---</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t xml:space="preserve">    TRUE</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">    instagram</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>13</v>
-      </c>
+          <t>--- platform distribution ---</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
+          <t xml:space="preserve">    instagram</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -8815,155 +9679,155 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>--- language distribution ---</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t xml:space="preserve">    (none)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    en</t>
+          <t xml:space="preserve">    facebook</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">    hi</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>3</v>
-      </c>
+          <t>--- language distribution ---</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    hi-en-mixed</t>
+          <t xml:space="preserve">    en</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>--- split distribution ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t xml:space="preserve">    hi</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    validation</t>
+          <t xml:space="preserve">    hi-en-mixed</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>9</v>
-      </c>
+          <t>--- split distribution ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- benchmark_version distribution ---</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t xml:space="preserve">    validation</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    v2</t>
+          <t xml:space="preserve">    (none)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    v1</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>9</v>
-      </c>
+          <t>--- benchmark_version distribution ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>--- claim_type distribution ---</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t xml:space="preserve">    v2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    provenance</t>
+          <t xml:space="preserve">    v1</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    misleading_context</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>2</v>
-      </c>
+          <t>--- claim_type distribution ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    visual</t>
+          <t xml:space="preserve">    provenance</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">    event</t>
+          <t xml:space="preserve">    misleading_context</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    quote</t>
+          <t xml:space="preserve">    visual</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -8973,103 +9837,103 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>--- media (video/photo) distribution ---</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t xml:space="preserve">    event</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    video</t>
+          <t xml:space="preserve">    quote</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    photo</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>3</v>
-      </c>
+          <t>--- media (video/photo) distribution ---</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>--- factchecker distribution ---</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t xml:space="preserve">    video</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    altnews.in</t>
+          <t xml:space="preserve">    photo</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    boomlive.in</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>4</v>
-      </c>
+          <t>--- factchecker distribution ---</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:boomlive.in</t>
+          <t xml:space="preserve">    altnews.in</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:altnews.in</t>
+          <t xml:space="preserve">    boomlive.in</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:factly.in</t>
+          <t xml:space="preserve">    tier-1-source:boomlive.in</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:boomlive.in (hindi.boomlive.in)</t>
+          <t xml:space="preserve">    tier-1-source:altnews.in</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:altnews.in (hindi.altnews.in)</t>
+          <t xml:space="preserve">    tier-1-source:factly.in</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -9079,7 +9943,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    thequint.com</t>
+          <t xml:space="preserve">    tier-1-source:boomlive.in (hindi.boomlive.in)</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -9089,7 +9953,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    vishvasnews.com</t>
+          <t xml:space="preserve">    tier-1-source:altnews.in (hindi.altnews.in)</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -9099,35 +9963,37 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>--- ground-truth tier distribution ---</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t xml:space="preserve">    thequint.com</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
+          <t xml:space="preserve">    vishvasnews.com</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1</t>
+          <t xml:space="preserve">    leadstories.com</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>--- difficulty distribution ---</t>
+          <t>--- ground-truth tier distribution ---</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -9139,41 +10005,41 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>--- annotation_status distribution ---</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t xml:space="preserve">    1</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>17</v>
-      </c>
+          <t>--- difficulty distribution ---</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier1_professional</t>
+          <t xml:space="preserve">    (none)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>--- modality availability (true count) ---</t>
+          <t>--- annotation_status distribution ---</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -9181,75 +10047,75 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    audio_available</t>
+          <t xml:space="preserve">    (none)</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ocr_available</t>
+          <t xml:space="preserve">    tier1_professional</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    caption_available</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>16</v>
-      </c>
+          <t>--- modality availability (true count) ---</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    visual_information_available</t>
+          <t xml:space="preserve">    audio_available</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>--- cross-post ---</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
+          <t xml:space="preserve">    ocr_available</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    cross_post_possible = true</t>
+          <t xml:space="preserve">    caption_available</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    cross_post_verified = true</t>
+          <t xml:space="preserve">    visual_information_available</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>--- missing-field rates ---</t>
+          <t>--- cross-post ---</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -9257,72 +10123,100 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no factcheck_url</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>0/26 (0%)</t>
-        </is>
+          <t xml:space="preserve">    cross_post_possible = true</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no publication_date</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>17/26 (65%)</t>
-        </is>
+          <t xml:space="preserve">    cross_post_verified = true</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no media_hash</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>9/26 (34%)</t>
-        </is>
-      </c>
+          <t>--- missing-field rates ---</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no split</t>
+          <t xml:space="preserve">    no factcheck_url</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9/26 (34%)</t>
+          <t>0/34 (0%)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no difficulty</t>
+          <t xml:space="preserve">    no publication_date</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>26/26 (100%)</t>
+          <t>25/34 (73%)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t xml:space="preserve">    no media_hash</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>9/34 (26%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    no split</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>9/34 (26%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    no difficulty</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>34/34 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
           <t xml:space="preserve">    no candidate_id (provenance)</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>9/26 (34%)</t>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>9/34 (26%)</t>
         </is>
       </c>
     </row>
@@ -11379,9 +12273,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>item-0032, item-0033</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>same content_hash on &gt;1 item -- repost/cross-post; keep + flag, do not delete</t>

--- a/research/dataset/TruthLens_Dataset.xlsx
+++ b/research/dataset/TruthLens_Dataset.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07T15:38:20+00:00</t>
+          <t>2026-09-07T17:17:45+00:00</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>9ab9768</t>
+          <t>a97658e</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK35"/>
+  <dimension ref="A1:AK48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3413,6 +3413,11 @@
           <t>altnews.in</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>claim flagged for rewrite: claim &gt;22 words -- likely raw caption/article paragraph</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr">
         <is>
           <t>https://www.altnews.in/bjp-media-outlets-share-holi-video-as-people-celebrating-bjp-victory-in-bengal/</t>
@@ -3446,6 +3451,11 @@
           <t>0b7ef784b46ebf3103b21b7c4c70d46bbfd241efc2afa4d93daac912443060cf</t>
         </is>
       </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>candidates_v3_altnews.jsonl</t>
@@ -3832,7 +3842,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3843,6 +3853,11 @@
       <c r="P29" t="inlineStr">
         <is>
           <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>label inferred (FALSE) from fact-check slug -- NEEDS HUMAN CONFIRMATION</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3878,6 +3893,11 @@
           <t>ce0e74bf0e7f76bf93acfd65bd4ba62b751ff8a7e151d304ca05a7bc178c4da3</t>
         </is>
       </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
       <c r="AJ29" t="inlineStr">
         <is>
           <t>candidates_v3_altnews.jsonl</t>
@@ -3940,7 +3960,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>MISLEADING</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3953,6 +3973,11 @@
           <t>altnews.in</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>label inferred (MISLEADING) from fact-check slug -- NEEDS HUMAN CONFIRMATION</t>
+        </is>
+      </c>
       <c r="T30" t="inlineStr">
         <is>
           <t>https://www.altnews.in/old-video-of-aviation-minister-k-r-naidu-dancing-falsely-viral-amid-indigo-crisis/</t>
@@ -3984,6 +4009,11 @@
       <c r="AF30" t="inlineStr">
         <is>
           <t>127ecea126d89ac271dab414e69d52e400ae5876abe319897479152099993014</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>needs_review</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -4156,7 +4186,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -4167,6 +4197,11 @@
       <c r="P32" t="inlineStr">
         <is>
           <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>label inferred (FALSE) from fact-check slug -- NEEDS HUMAN CONFIRMATION</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -4202,6 +4237,11 @@
           <t>964b903e31486376a95b3a9b7b182d72568a50e195ee17dd24960fa3b4cc9c2f</t>
         </is>
       </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
       <c r="AJ32" t="inlineStr">
         <is>
           <t>candidates_v3_altnews.jsonl</t>
@@ -4264,7 +4304,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>MISLEADING</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4275,6 +4315,11 @@
       <c r="P33" t="inlineStr">
         <is>
           <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>label inferred (MISLEADING) from fact-check slug -- NEEDS HUMAN CONFIRMATION</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -4310,6 +4355,11 @@
           <t>6b3c402e397a12bad8a3cbbe7d7ab1c9d144b94f6724e18b87ca583f6782e990</t>
         </is>
       </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>candidates_v3_altnews.jsonl</t>
@@ -4372,7 +4422,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>MISLEADING</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -4383,6 +4433,11 @@
       <c r="P34" t="inlineStr">
         <is>
           <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>label inferred (MISLEADING) from fact-check slug -- NEEDS HUMAN CONFIRMATION</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -4418,6 +4473,11 @@
           <t>6b3c402e397a12bad8a3cbbe7d7ab1c9d144b94f6724e18b87ca583f6782e990</t>
         </is>
       </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>candidates_v3_altnews.jsonl</t>
@@ -4480,7 +4540,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -4493,6 +4553,11 @@
           <t>leadstories.com</t>
         </is>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>label inferred (FALSE) from fact-check slug -- NEEDS HUMAN CONFIRMATION</t>
+        </is>
+      </c>
       <c r="T35" t="inlineStr">
         <is>
           <t>https://leadstories.com/hoax-alert/2020/06/fact-check-atlanta-did-not-deploy-a-child-militia-during-protests.html</t>
@@ -4526,6 +4591,11 @@
           <t>4b48a848c5f05592dadb58da56db7e9f10ff3752cbef3e5d9b806519bb69c622</t>
         </is>
       </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
       <c r="AJ35" t="inlineStr">
         <is>
           <t>candidates_v3_leadstories.jsonl</t>
@@ -4534,6 +4604,1575 @@
       <c r="AK35" t="inlineStr">
         <is>
           <t>2026-09-07T14:37:22.560671+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>item-0035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0657</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://twitter.com/amitmalviya/status/1970793380016701713</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/ladakh-violence-bjp-falsely-claims-armed-man-in-viral-footage-is-congress-councillor-phuntsog-stanzin-tsepag/</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>This claim was amplified by several BJP ministers and Right-wing influencers, including Amit Malviya (@amitmalviya), Kanchan Gupta ( @KanchanGupta ), Nishikant Dubey (@nishikant_dubey) who tweeted the same image of Phuntsog Stanzin Tsepag wearing a beige coat with a firearm in hand. The claim was also amplified by OpIndia and Right-wing X users, including Vijay Patel ( @vijaygajera )</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>claim flagged for rewrite: claim &gt;22 words -- likely raw caption/article paragraph</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/ladakh-violence-bjp-falsely-claims-armed-man-in-viral-footage-is-congress-councillor-phuntsog-stanzin-tsepag/</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W36" t="b">
+        <v>1</v>
+      </c>
+      <c r="X36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>3fb7a631554448b5ab3e080f7b2171b1fbdf32ad386805d7bcbd3395e43cec2f</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:52:52.361376+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>item-0036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0682</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Sheetal2242/status/1970291388689600638</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/success-of-demonetisation-video-of-kids-flaunting-old-demonetised-notes-not-from-pakistan-but-lucknow/</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>पाकिस्तान में हमारे पुराने 500 रुपये के भारतीय नोट..।।  कागज़ बेचने वाले लड़के अपने कचड़ा ठेले पर इन्हें लहरा रहे हैं।  अब सवाल ये है कि पाकिस्तान में इतने अधिक मात्रा में भारतीय नोट कैसे पहुंच.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>label inferred (FALSE) from fact-check slug -- NEEDS HUMAN CONFIRMATION | claim flagged for rewrite: claim &gt;22 words -- likely raw caption/article paragraph</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/success-of-demonetisation-video-of-kids-flaunting-old-demonetised-notes-not-from-pakistan-but-lucknow/</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W37" t="b">
+        <v>1</v>
+      </c>
+      <c r="X37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>0d4c20941d70b4b695801a9298a0de5b7760db84850888e07105d9c24522c9e2</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>needs_review</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:00:13.027721+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>item-0037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0839</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://twitter.com/jayanta_malla/status/1950893741033791789</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/ai-generated-video-shared-to-falsly-claim-bilawal-bhutto-said-our-agents-are-sitting-in-their-parliament/</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Our people are sitting in India's Parliament – Bilawal Bhutto.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/ai-generated-video-shared-to-falsly-claim-bilawal-bhutto-said-our-agents-are-sitting-in-their-parliament/</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="b">
+        <v>1</v>
+      </c>
+      <c r="X38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>43a15e16b0eec86573a1a24d057c99e34e7ca1811f5c9ac424e2f5bd95928f3b</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:39:46.428469+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>item-0038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0873</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://twitter.com/MeghUpdates/status/1949540048103420014</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/man-who-shouted-allah-hu-akbar-death-to-trump-on-uk-flight-is-a-hindu/</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>A man who shouted “Allahu Akbar” and threats against Trump on a UK-bound flight and was restrained by passengers is a Muslim (and a Pakistani).</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Alt News identified the man as a Hindu; article title: “Man who shouted ‘Allah Hu Akbar’, ‘Death to Trump’ on UK flight is a Hindu”. The Muslim/Pakistani identity claim is fabricated.</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/man-who-shouted-allah-hu-akbar-death-to-trump-on-uk-flight-is-a-hindu/</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>574383aa7cadbac3a17b9b80bae59c79c87c11f2684097e7ee66f3e471842495</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:44:09.339501+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>item-0039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0913</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Shehzad_Ind/status/1942919166534812033</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/after-cong-leader-pappu-yadav-stopped-from-entering-rahul-gandhi-tejashwis-car-in-bihar-old-video-of-him-crying-viral/</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Pappu Yadav</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>A video of Congress leader Pappu Yadav crying in a car shows his reaction to being stopped from joining Rahul Gandhi and Tejashwi Yadav's vehicle at a July 9, 2025 rally in Bihar.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Alt News: the crying video is OLD and unrelated to the July 9 incident (article title: “...old video of him crying viral”). Yadav himself later said the July 9 stop was security protocol, not an insult.</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/after-cong-leader-pappu-yadav-stopped-from-entering-rahul-gandhi-tejashwis-car-in-bihar-old-video-of-him-crying-viral/</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W40" t="b">
+        <v>1</v>
+      </c>
+      <c r="X40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>748f16b44f676288011484fe21011e2738797981eb7be6e84d0c507c34ae71e5</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:54:56.260713+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>item-0040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0943</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/61568720176479/videos/695192180041019</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/old-and-unrelated-videos-shared-as-bhim-army-chandrashekhar-raavan-supporters-in-prayagraj/</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Chandrashekhar Azad</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Viral videos show supporters of Chandrashekhar Azad / Bhim Army who rioted in Prayagraj being beaten and punished by Uttar Pradesh police.</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Alt News: the two videos are OLD and UNRELATED to the June 29 Prayagraj protest (article title: “Old and unrelated videos shared as Bhim Army... supporters in Prayagraj”).</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/old-and-unrelated-videos-shared-as-bhim-army-chandrashekhar-raavan-supporters-in-prayagraj/</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W41" t="b">
+        <v>1</v>
+      </c>
+      <c r="X41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD41" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>036880acb3ecc391f4ef3d98d54ff21aba3d763ef7a8a9724ee76c7519d550c7</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:59:49.488117+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>item-0041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0949</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>https://twitter.com/SonOfBharat7/status/1942096708126593260</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/did-pakistan-zindabad-slogan-raise-in-deoria-up-during-muharram-procession/</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>‘Pakistan Zindabad’ slogans were raised by Muslims during a Muharram procession in Deoria, Uttar Pradesh.</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Alt News: the official Deoria Police X handle refuted the claim; the slogans in the procession video were by the 'Five Star Club', not 'Pakistan Zindabad'.</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/did-pakistan-zindabad-slogan-raise-in-deoria-up-during-muharram-procession/</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="W42" t="b">
+        <v>1</v>
+      </c>
+      <c r="X42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD42" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>b592b2627de5b10f77de7e947eefa7b21a66a43bd57aedd3e4e212ce772f1875</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:02:00.427772+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>item-0042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0955</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>https://twitter.com/erbmjha/status/1940447650127687683</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-hindu-woman-kneeling-at-rath-yatra-in-puri-viral-with-false-claims-that-she-was-offering-namaz/</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>A video from the Puri Rath Yatra shows a Muslim woman deliberately offering namaz (Islamic prayer) under the Jagannath chariot to disrespect Hindu religious sentiment.</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Alt News: the woman is Hindu and was kneeling/being pulled away by a female police volunteer, not offering namaz; the clip does not show namaz being offered.</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-hindu-woman-kneeling-at-rath-yatra-in-puri-viral-with-false-claims-that-she-was-offering-namaz/</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W43" t="b">
+        <v>1</v>
+      </c>
+      <c r="X43" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>14f7bb56b3b23fd3699c9bb2e53614766dda045a3f431ec9addb45e864099761</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:03:14.236098+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>item-0043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0961</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://twitter.com/MrSinha_/status/1941444953080725842</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/rahul-gandhis-photo-on-sanitary-pads-distributed-in-bihar-congress-files-fir-over-fake-video/</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>The Bihar unit of the Congress party is distributing sanitary napkins with Rahul Gandhi's photo printed on the packaging and on the pads themselves.</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Alt News: the video is fabricated/edited; Bihar Congress filed an FIR over the fake video. The real napkin packs distributed in the campaign do not carry Rahul Gandhi's image on the pads.</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/rahul-gandhis-photo-on-sanitary-pads-distributed-in-bihar-congress-files-fir-over-fake-video/</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="W44" t="b">
+        <v>1</v>
+      </c>
+      <c r="X44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>829ddfba6d6847a49282fb5e3d81de92242cb4aee3f65248e714fa71cc235009</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:05:44.975200+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>item-0044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0965</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://twitter.com/PoddarVaishali/status/1938818981927772411</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/false-claim-of-person-wearing-a-garland-of-slippers-in-bangladesh-is-hindu-teacher-fact-check/</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>A video of a man garlanded with slippers by a Muslim crowd in Bangladesh shows a Hindu teacher who served the country for 40 years being humiliated by fundamentalists.</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Alt News: the man in the video is not a Hindu teacher; the 'Hindu teacher who served 40 years' identity is fabricated (article title: 'False claim of person wearing a garland of slippers in Bangladesh is Hindu teacher').</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/false-claim-of-person-wearing-a-garland-of-slippers-in-bangladesh-is-hindu-teacher-fact-check/</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W45" t="b">
+        <v>1</v>
+      </c>
+      <c r="X45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD45" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>5121dc7c9381f67ca59608114c3e70d6fe52a766f4f5adc87705f3863b454dec</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:07:14.813393+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>item-0045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0991</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://twitter.com/NavrtnYadav/status/1939360173342261413</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/dalit-man-tortured-in-jhansi-old-video-resurfaces-police-says-victim-assailants-from-same-community/</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>BJP</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>A video shows a Dalit labourer in Jhansi, Uttar Pradesh having his head forcibly shaved and being paraded as caste-based humiliation for refusing work — a 'Taliban-like' atrocity under the BJP government.</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Alt News: the clip is an OLD video that resurfaced; Jhansi police stated the victim and the assailants are from the same community, so the caste-atrocity / 'BJP government Taliban punishment' framing is a misrepresentation.</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/dalit-man-tortured-in-jhansi-old-video-resurfaces-police-says-victim-assailants-from-same-community/</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W46" t="b">
+        <v>1</v>
+      </c>
+      <c r="X46" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD46" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>fa14d1c00af2fa6a334a03ff6e81debf8a349582593ca527f0c49dcbbfb68678</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:15:03.734204+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>item-0046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0998</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>https://twitter.com/iAnonPatriot/status/1938295539113611452</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-from-2023-pro-palestine-protest-viral-with-misleading-claims-that-muslims-are-ripping-us-flags-in-nyc/</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Zohran Mamdani</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>A video shows Muslims in New York City tearing down American flags after Zohran Mamdani's win in the NYC Democratic mayoral primary.</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Alt News: the footage is from a November 2023 pro-Palestine protest in NYC (matched via reverse image search to a Nov 12 2023 YouTube upload). It predates the Mamdani primary by ~19 months and the 'Muslims' framing is unsupported.</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-from-2023-pro-palestine-protest-viral-with-misleading-claims-that-muslims-are-ripping-us-flags-in-nyc/</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W47" t="b">
+        <v>1</v>
+      </c>
+      <c r="X47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD47" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>09a96a9ac07587b91e3017776ba9b7406979f19cc562fa52e31d97daedfc17ee</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:35:43.830335+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>item-0047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1004</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://twitter.com/geetappoo/status/1936863809672786233</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/2021-video-from-delhis-yamuna-vihar-viral-with-misleading-claims-of-communal-disharmony/</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>A video of an injured, blood-stained family shows a Muslim family in Delhi's Yamuna Vihar being beaten by Hindus for asking them to switch off loudspeakers at a Hindu religious event.</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Alt News: the video is from 2021 and is being recirculated with a false current communal framing (article title: '2021 video from Delhi's Yamuna Vihar viral with misleading claims of communal disharmony').</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/2021-video-from-delhis-yamuna-vihar-viral-with-misleading-claims-of-communal-disharmony/</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W48" t="b">
+        <v>1</v>
+      </c>
+      <c r="X48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD48" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>77dad4d7fdf45c62ad7958dc6501df584186e744d80a557ec40468e19fd88bea</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:38:07.793936+00:00</t>
         </is>
       </c>
     </row>
@@ -4548,7 +6187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:P78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7072,7 +8711,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7099,7 +8738,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>MISLEADING</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7153,7 +8792,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7180,7 +8819,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>MISLEADING</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7207,7 +8846,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>MISLEADING</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7234,10 +8873,361 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>item-0035</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>This claim was amplified by several BJP ministers and Right-wing influencers, including Amit Malviya (@amitmalviya), Kanchan Gupta ( @KanchanGupta ), Nishikant Dubey (@nishikant_dubey) who tweeted the same image of Phuntsog Stanzin Tsepag wearing a beige coat with a firearm in hand. The claim was also amplified by OpIndia and Right-wing X users, including Vijay Patel ( @vijaygajera )</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>item-0036</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>पाकिस्तान में हमारे पुराने 500 रुपये के भारतीय नोट..।।  कागज़ बेचने वाले लड़के अपने कचड़ा ठेले पर इन्हें लहरा रहे हैं।  अब सवाल ये है कि पाकिस्तान में इतने अधिक मात्रा में भारतीय नोट कैसे पहुंच.</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>item-0037</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Our people are sitting in India's Parliament – Bilawal Bhutto.</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>item-0038</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>A man who shouted “Allahu Akbar” and threats against Trump on a UK-bound flight and was restrained by passengers is a Muslim (and a Pakistani).</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>item-0039</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>A video of Congress leader Pappu Yadav crying in a car shows his reaction to being stopped from joining Rahul Gandhi and Tejashwi Yadav's vehicle at a July 9, 2025 rally in Bihar.</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>item-0040</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Viral videos show supporters of Chandrashekhar Azad / Bhim Army who rioted in Prayagraj being beaten and punished by Uttar Pradesh police.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>item-0041</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>‘Pakistan Zindabad’ slogans were raised by Muslims during a Muharram procession in Deoria, Uttar Pradesh.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>item-0042</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>A video from the Puri Rath Yatra shows a Muslim woman deliberately offering namaz (Islamic prayer) under the Jagannath chariot to disrespect Hindu religious sentiment.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>item-0043</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>The Bihar unit of the Congress party is distributing sanitary napkins with Rahul Gandhi's photo printed on the packaging and on the pads themselves.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>item-0044</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>A video of a man garlanded with slippers by a Muslim crowd in Bangladesh shows a Hindu teacher who served the country for 40 years being humiliated by fundamentalists.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>item-0045</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>A video shows a Dalit labourer in Jhansi, Uttar Pradesh having his head forcibly shaved and being paraded as caste-based humiliation for refusing work — a 'Taliban-like' atrocity under the BJP government.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>item-0046</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>A video shows Muslims in New York City tearing down American flags after Zohran Mamdani's win in the NYC Democratic mayoral primary.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>item-0047</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>A video of an injured, blood-stained family shows a Muslim family in Delhi's Yamuna Vihar being beaten by Hindus for asking them to switch off loudspeakers at a Hindu religious event.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>provenance</t>
         </is>
@@ -7254,7 +9244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7267,7 +9257,7 @@
     <col width="35" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
     <col width="60" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
@@ -8690,6 +10680,11 @@
           <t>cand-ap-altnews-0657</t>
         </is>
       </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>item-0035</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -8755,6 +10750,11 @@
           <t>cand-ap-altnews-0682</t>
         </is>
       </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>item-0036</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -8817,12 +10817,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0021</t>
+          <t>cand-ap-altnews-0839</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>item-0034</t>
+          <t>item-0037</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8832,7 +10832,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -8842,22 +10842,22 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://twitter.com/foxwoundband/status/1266613385862447104</t>
+          <t>https://twitter.com/jayanta_malla/status/1950893741033791789</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-atlanta-did-not-deploy-a-child-militia-during-protests.html</t>
+          <t>https://www.altnews.in/ai-generated-video-shared-to-falsly-claim-bilawal-bhutto-said-our-agents-are-sitting-in-their-parliament/</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-09-07T14:37:22.560671+00:00</t>
+          <t>2026-09-07T15:39:46.428469+00:00</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -8870,24 +10870,24 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Atlanta has deployed a child militia at Lenox Mall fitted with riot shields and batons.</t>
+          <t>Our people are sitting in India's Parliament – Bilawal Bhutto.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The post's own caption/text states the debunked claim that Atlanta deployed 'a child militia' during recent protests.</t>
+          <t>llama3.2 (conf=1.00): The post's own caption states the false claim made by Bilawall Bhuttospeech in the viral video.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0057</t>
+          <t>cand-ap-altnews-0871</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -8897,32 +10897,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=3fu6Bo-uMEE</t>
+          <t>https://twitter.com/Basil_TGMD/status/1949482415766053338</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-gates-dr-fauci-and-the-cdc-not-silent-on-protests-riots.html</t>
+          <t>https://www.altnews.in/man-who-shouted-allah-hu-akbar-death-to-trump-on-uk-flight-is-a-hindu/</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-09-07T14:42:36.244282+00:00</t>
+          <t>2026-09-07T15:44:09.331630+00:00</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -8931,7 +10931,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.9999979556447476</v>
+        <v>1</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -8940,21 +10940,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>If you're not sick, everytime you put your mask on, the same masks worn by ANTIFA terrorists, you are allowing them to control you.</t>
+          <t>Muslim Man on a flight to Glasgow screaming “allahu akbar”, threatening to bomb the plane. Are you feeling culturally enriched yet?</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): [This is the case we are collecting.] The post itself makes the debunked claim that all of these people (Gates, Fauci, Birx) have stayed silent amid protests sparked by George Floyd's death.
-The article debunks this claim and provides evidence from various sources showing they have spoken out about the protests. This includes a transcript of an interview with Dr. Deborah Birx on PBS where she expresses concern over peaceful protesters not wearing masks and calls for expanded testing availability, as well as tweets by Bill Gates' wife Melinda supporting those protesting.
-The post is wrong because it asserts that these individuals have stayed silent amid protests sparked by George Floyd's death when in fact they have spoken out about the issue.</t>
+          <t>llama3.2 (conf=1.00): [This] The post explicitly states that the man on the flight to Glasgow screamed “allahu akbar”, threatening to bomb the plane and ranted about Trump. This claim is false as Abhay Nayak was identified in BBC reports, prominent media outlets, including The Times of India, The Telegraph, Deccan Herald, and Sky News,  as a Hindu resident named Abhay Devdas Nayak.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0212</t>
+          <t>cand-ap-altnews-0872</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -8964,32 +10962,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=J0CLMqpsrgY</t>
+          <t>https://twitter.com/Incognito_qfs/status/1949551127843721238</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-doctors-do-recommend-vitamins-and-sunlight-for-peoples-health.html</t>
+          <t>https://www.altnews.in/man-who-shouted-allah-hu-akbar-death-to-trump-on-uk-flight-is-a-hindu/</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-09-07T15:05:48.862967+00:00</t>
+          <t>2026-09-07T15:44:09.337287+00:00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -8998,28 +10996,33 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>'almost no evidence' is a misrepresentation of Dr Belchetz statement that 'there are many studies showing benefits to taking vitamins and supplements', according to the CBC article.</t>
+          <t>He was a Muslim person who was on a flight to Glasgow.</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=0.90): The original claim made in this post's caption states that 'almost no evidence backs up claims from vitamin and supplement industry'. However, according to Dr Belchetz' statement cited on YouTube (referenced by the same source as CBC article), there are many studies showing benefits of taking vitamins. The use of the term "almost" is misleading because it implies a lack of any evidence when in fact multiple researches support its claims.</t>
+          <t>llama3.2 (conf=1.00): According to the fact-check article, it was found out by Alt News investigation that 'the individual [Abhay Devdas Nayak]... has not been charged with terrorism...' and he 'has not been identified as a Muslim'. The post's caption claims Abhay is a Muslim person on a flight to Glasgow. This claim contradicts the fact-check article findings.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0223</t>
+          <t>cand-ap-altnews-0873</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>item-0038</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -9029,32 +11032,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=ad1ysX2iLmA</t>
+          <t>https://twitter.com/MeghUpdates/status/1949540048103420014</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-birth-certificate-does-not-prove-donald-trump-had-son-with-ghislaine-maxwell.html</t>
+          <t>https://www.altnews.in/man-who-shouted-allah-hu-akbar-death-to-trump-on-uk-flight-is-a-hindu/</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-09-07T15:08:10.465015+00:00</t>
+          <t>2026-09-07T15:44:09.339501+00:00</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -9067,24 +11070,24 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>The @realJimmyTrump account has recently changed its photo from a picture of Kieran Culkin to the Birth Certificate and a meme image known as "Zuckertrump." The identity of Rogue WH Snr Advisor remains unknown, but they are most certainly not the son of President Trump and Ghislaine Maxwell.</t>
+          <t>A Muslim on a flight to Glasgow screaming “allahu akbar”, threatening to bomb the plane and ranting about Trump.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The post's caption changes the image on @realJimmyTrump account from a picture of Kieran Culkin to one that includes the Birth Certificate with 'Zuckertrump' meme, which is an edited version of Donald Trump and implies he was involved in some scandalous activity (sex offender) but does not state it directly. The post's caption also says Rogue WH Snr Advisor are most certainly NOT Ghislaine Maxwell &amp; President trump son - making this claim MISINFORMATION_SOURCE.</t>
+          <t>llama3.2 (conf=1.00): The post's caption states the debunked claim made in the fact-check article: that the person is Muslim and Pakistani. However, according to the article, the individual was identified as Abhay Devdas Nayak, a man of Indian origin.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0245</t>
+          <t>cand-ap-altnews-0887</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -9094,32 +11097,32 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=TYfXE8QeFHE</t>
+          <t>https://twitter.com/vinushareddyb/status/1947659232813387834</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-clark-hunt-did-not-threaten-to-fire-his-players-and-staff-if-they-dont-stand-for-the-national-anthem.html</t>
+          <t>https://www.altnews.in/poor-should-remain-poor-bengal-bjp-shares-clipped-video-distorting-context-of-mamatas-2024-martyrs-day-remarks/</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-09-07T15:09:56.550526+00:00</t>
+          <t>2026-09-07T15:49:21.302808+00:00</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -9128,7 +11131,7 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -9137,19 +11140,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>'You are all simply paid performers on a stage and that field is my stage! You will stand, with your hand over your heart and with respect, when our Country's National Anthem is being played or you will no longer be a Kansas City Chief, a Coach for the Kansas City Chiefs or have any association with the Chiefs Organization!'</t>
+          <t>'I want you to stay poor.' Whatever food you have at your home, eat and survive'</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The caption of this YouTube post is identical to the claim mentioned at the beginning of the fact-check article, which was debunked as a false attribution to Clark Hunt and other NFL owners.</t>
+          <t>llama3.2 (conf=0.90): The caption of the post directly states a false claim made by Mamata Banerjee in an out-of-context manner.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0273</t>
+          <t>cand-ap-altnews-0898</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -9159,32 +11162,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=WvKSy1bwT70</t>
+          <t>https://www.facebook.com/reel/707531534863299</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-the-cdc-does-recommend-buying-and-using-face-masks-even-if-you-are-healthy.html</t>
+          <t>https://www.altnews.in/screenshots-from-a-scripted-video-shared-with-false-claim-that-72-years-old-man-married-21-years-old-girl/</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-09-07T15:17:06.077762+00:00</t>
+          <t>2026-09-07T15:52:49.794402+00:00</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -9193,28 +11196,24 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Yes, this is a real flyer,</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The post's caption states that President Trump announced the CDC is changing its guidelines to recommend people wear simple cloth face masks, which includes a claim about healthy individuals not needing to buy or use face masks. This matches with what was stated in an outdated Delaware Health and Social Services infographic published March 2020.</t>
+          <t>llama3.2 (conf=0.90): The Facebook post itself states '70 साल के बुड्ढे ने की 18 साल की लड़की से शादी' (A 70-year-old man married an 18-year-old girl), which is the same claim made by other social media users and debunked in the fact-check article as part of a scripted video. The post's caption does not provide any additional context or clarify that it is referring to a different incident, making it clear that this is indeed the false claim being referred to.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0314</t>
+          <t>cand-ap-altnews-0908</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9224,32 +11223,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=VhirLohgDRc</t>
+          <t>https://twitter.com/mRupeshVerma/status/1942534356423315824</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/07/fact-check-no-evidence-european-royals-are-hunting-naked-children-for-fun-at-human-hunting-parties.html</t>
+          <t>https://www.altnews.in/claim-that-india-has-invented-a-self-sustaining-generator-that-runs-for-700-years-without-power-fuel-is-fabricated/</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-09-07T15:25:59.766110+00:00</t>
+          <t>2026-09-07T15:53:59.715900+00:00</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -9258,33 +11257,28 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>European royals killing naked children for fun at human hunting parties.</t>
+          <t>अब आप अपने जीवन में कभी भी अंधेरा नहीं देख सकेंगे, अब कभी लाइट बंद नहीं होगी, और न ही लाइट जायेगी।</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The caption of this YouTube post directly links to the same source (Kevin Annetts' blog) which originally published and promoted the debunked claim. The text itself is a direct copy from Kevin Annett's video, making no distinction between fact or fiction.</t>
+          <t>llama3.2 (conf=0.99): The post's caption states a false and unsubstantiated claim about India inventing a magnetic power generator under Modi's government, which is explicitly debunked in the fact-check article.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cand-mass-0027</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>item-0019</t>
+          <t>cand-ap-altnews-0909</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -9297,56 +11291,64 @@
           <t>altnews.in</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DX7LBwesE-o/</t>
+          <t>https://www.youtube.com/watch?v=Hm_cSmvmIXs</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.altnews.in/bjp-media-outlets-share-holi-video-as-people-celebrating-bjp-victory-in-bengal/</t>
+          <t>https://www.altnews.in/claim-that-india-has-invented-a-self-sustaining-generator-that-runs-for-700-years-without-power-fuel-is-fabricated/</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>candidates_v2.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-08-18T00:59:01.077843+00:00</t>
+          <t>2026-09-07T15:53:59.733043+00:00</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
-        </is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.99</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False claim: The post's own caption asserts that it depicts people celebrating a political event (BJP victory), but actually shows a pre-election celebration during Holi.</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Celebrations of Jai Sri Ram at the Holi celebrations in Kolkata, which took place two months before May 4th</t>
+          <t>मोदीजी है तो सबकुछ मुमकिन है, कभी लाइट बंद नहीं होगी, और ना ही लाइट जायेगी।</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>llama3.2 judge (confidence=0.90): The Instagram Post’s Own Caption Asserts the False Claim</t>
+          <t>llama3.2 (conf=0.99): The post's caption states the false claim that India invented a 'self-sustaining' magnetic power generator under the Narendra Modi-led BJP government, which is debunked by the fact-check article as baseless and fabricated.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cand-mass-0088</t>
+          <t>cand-ap-altnews-0911</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ELIGIBLE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9354,47 +11356,64 @@
           <t>altnews.in</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DPcCJWxga06/</t>
+          <t>https://twitter.com/Bitt2DA/status/1942899035616256163</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.altnews.in/yogi-adityanath-left-to-hear-criticism-of-govt-while-ravi-kishan-was-enjoying-doctored-video-viral/</t>
+          <t>https://www.altnews.in/after-cong-leader-pappu-yadav-stopped-from-entering-rahul-gandhi-tejashwis-car-in-bihar-old-video-of-him-crying-viral/</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>candidates_v2.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-08-18T01:51:54.674020+00:00</t>
+          <t>2026-09-07T15:54:56.252137+00:00</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; REJECTED</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Judged NOT the misinformation source (confidence=1.00): </t>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>किस ने इसी तरह से मारा?  बाघ का करेजा का ये हाल है बिहार में?</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption of the post states: 'पप्पू यादव की आँखों में आँसू क्यों है?   किसने इसकी बेइज्जती की है? कोई बताएगा' which is identical to the false claim mentioned in the fact-check article. The post's caption directly states that Pappu Yadav was 'मारा' (attacked) by a group of people, but according to the fact check, it was Congress leader Pappu Yadav who alleged that he and others were abused and physically assaulted during an attack on September 6, 2018. The post's caption is essentially repeating the false claim made in social media.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cand-thequint-0182</t>
+          <t>cand-ap-altnews-0913</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>item-0021</t>
+          <t>item-0039</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -9404,107 +11423,3274 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>thequint.com</t>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DRmx_YwjN7Y/</t>
+          <t>https://twitter.com/Shehzad_Ind/status/1942919166534812033</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.thequint.com/news/webqoof/ai-generated-yogi-lifting-weighting-without-his-hands-fact-check</t>
+          <t>https://www.altnews.in/after-cong-leader-pappu-yadav-stopped-from-entering-rahul-gandhi-tejashwis-car-in-bihar-old-video-of-him-crying-viral/</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>candidates_v2_mass_thequint.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-08-18T05:29:58.023010+00:00</t>
+          <t>2026-09-07T15:54:56.260713+00:00</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; ELIGIBLE</t>
-        </is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>1</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>INDIAN YOGI MOVES 95 Kgs of weight in the gym with his mind!</t>
-        </is>
-      </c>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>llama3.2 judge (confidence=1.00): The caption text itself makes a specific false assertion about lifting '130 kgs' (not mentioned) and claims that it's done using one's 'mind', which is the exact same claim being debunked in the article.. NOT yet human/manual-reviewed.</t>
+          <t>llama3.2 (conf=1.00): The post's caption, ' Bahut Bura hua Vro ', directly translates to 'Very Bad Happened' in English. This statement is the same false claim made by Congress leader Pappu Yadav during a viral video from September 6, 2018 (as debunked by fact-check article), which was later shared on social media with similar comments and claims about an alleged snub at Rahul Gandhi's rally.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>cand-ap-altnews-0914</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ajeetbharti/status/1942914368020086888</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/after-cong-leader-pappu-yadav-stopped-from-entering-rahul-gandhi-tejashwis-car-in-bihar-old-video-of-him-crying-viral/</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:54:56.263820+00:00</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=0.99): This post's caption directly states a false claim about when (July 9) and how (abused), which is contradicted by the fact-check article that confirms it happened in September of 2018.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0918</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=mtBEji1MwGQ</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/after-cong-leader-pappu-yadav-stopped-from-entering-rahul-gandhi-tejashwis-car-in-bihar-old-video-of-him-crying-viral/</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:55:01.091718+00:00</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption of the post states: 'बिहार के मधेपुरा से सांसद पप्पू यादव ने सवर्ण जातियों के भारत बंद के दौरान प्रदर्शनकारियों पर बड़ा आरोप लगाया है. #PappuYadav' This statement is the same as what was debunked in the fact-check article, which states that Pappu Yadav's claims of being attacked and abused by protesters were exaggerated. The caption directly repeats this claim without any clarification or context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0923</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://twitter.com/KumaarSaagar/status/1944224572653306128</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/glass-shards-on-kanwar-yatra-route-delhi-police-rubbishes-sabotage-communal-conspiracy-claims/</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:56:58.330438+00:00</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">दिल्ली के शाहदरा इलाक़े के अंदर बॉर्डर से लेकर क़रीब 1 किलोमीटर तक जिहादियों की ख़ौफ़नाक साज़िश। </t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption states that glass shards were scattered on the road in Dilshad Garden area 'क़रीब 1 किलोमीटर तक' (almost a kilometre) and also mentions 'जिहादियों की ख़ौफ़नाक साज़िश', which is an unsubstantiated claim. The article debunks this assertion by stating that the glass shards were accidentally broken while transporting them, not as part of any deliberate sabotage or conspiracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0924</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://twitter.com/LtGovDelhi/status/1944344678024818955</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/glass-shards-on-kanwar-yatra-route-delhi-police-rubbishes-sabotage-communal-conspiracy-claims/</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:56:58.334706+00:00</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>0.999995</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>large amount of shards of broken glass had been strewn on a stretch of about one km road in Dilshad Garden, on the route of Kaanwar Yatris</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): This classification was determined because the extracted claim in THIS post's own text matches exactly with what FACT-CHECK ARTICLE TEXT debunks as a false claim made by Kapil Mishra and other BJP leaders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0925</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://twitter.com/MrSinha_/status/1944235380074852583</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/glass-shards-on-kanwar-yatra-route-delhi-police-rubbishes-sabotage-communal-conspiracy-claims/</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:56:58.338695+00:00</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>some mischievous elements scattered glass pieces along the Kanwar Yatra route for nearly a kilometre.</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states that 'Bhaichara, anyone..??' which hints at alleged involvement of members of the Muslim community. This is in line with Kapil Mishra’s tweet where he claimed “some mischievous elements scattered glass pieces along the Kanwar Yatra route for nearly a kilometre.” (Archive) The article debunks this claim, stating that there was no evidence of sabotage or conspiracy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0926</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://twitter.com/OpIndia_com/status/1944261745520128404</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/glass-shards-on-kanwar-yatra-route-delhi-police-rubbishes-sabotage-communal-conspiracy-claims/</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:57:00.821359+00:00</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>glass shards were deliberately scattered along a 1.5 km stretch, posing a serious risk to devotees during the ongoing Kanwar Yatra.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=0.90):  The original text states 'Authorities are investigating the malicious act, while a separate case of ''thook jihad'' in Ghaziabad raises further concerns.' which is not present on this post's own caption/text and instead says </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0927</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://twitter.com/SudarshanNewsDL/status/1944224368500126192</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/glass-shards-on-kanwar-yatra-route-delhi-police-rubbishes-sabotage-communal-conspiracy-claims/</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:57:01.388317+00:00</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>दिल्ली के शाहदरा इलाक़े के अंदर जिहादियों की ख़ौफ़नाक साज़िश।  सावन के महीने के अंदर जब भोले नंगे पैर इसी रास्ते से जाना था।</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption states a claim that is debunked by the fact-check article, which attributes the broken glass shards to an e-rickshaw driver accidentally dropping them while transporting glass panels from Shalimar Garden to Seelampur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0943</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>item-0040</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/61568720176479/videos/695192180041019</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/old-and-unrelated-videos-shared-as-bhim-army-chandrashekhar-raavan-supporters-in-prayagraj/</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:59:49.488117+00:00</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Chandrashekhar Ravan’s supporters who rioted in Prayaggraj are getting the treatment they deserve from Yogi’s UP police.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0947</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=eRq8qS5jTOM</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/after-custodial-death-in-tamilnadu-video-from-up-viral-as-tamil-police-brutality/</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:01:08.928703+00:00</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>पहले थाना प्रभारी विनोद मिश्रा ने किसी काम के लिए युवक से पैसे लिए और जब पैसे देकर भी काम नहीं हुआ तो युवक पैसे मांगने पहुंचा, जिसके बाद दारोगा ने युवक को बुरी तरह से पीट दिय.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption of the YouTube post states that Vinod Mishra beat up a youth who demanded his money back after being cheated by him for some work.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0949</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>item-0041</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>https://twitter.com/SonOfBharat7/status/1942096708126593260</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/did-pakistan-zindabad-slogan-raise-in-deoria-up-during-muharram-procession/</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:02:00.427772+00:00</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>पाकिस्तान जिंदाबाद 🚨  जी हाँ ये पाकिस्तान जिंदabad क़े नारे लगाती ये भीड़ पाकिस्तान में नहीं भारत में है और भारत क़े भी उत्तर प्रदेश में है</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0950</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://twitter.com/BesuraTaansane/status/1940456534057931139</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-hindu-woman-kneeling-at-rath-yatra-in-puri-viral-with-false-claims-that-she-was-offering-namaz/</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:03:12.246445+00:00</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shameless beach was caught offering ⚠ under the Rath at the Jagannath Rath Yatra </t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption directly states that a woman (referred to as 'shameless beach') offered namaz underneath the chariot during the festival. This claim is debunked by fact-checkers in the article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0951</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>https://twitter.com/KumaarSaagar/status/1940465341576208618</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-hindu-woman-kneeling-at-rath-yatra-in-puri-viral-with-false-claims-that-she-was-offering-namaz/</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:03:12.251087+00:00</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption of this X user shares almost identical language to what FACT-CHECK ARTICLE TEXT debunks as MISINFORMATION_SOURCE: the post itself makes a false claim about namaz being offered under Jagannath's chariot during Rath Yatra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0952</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Lawyer_Kalpana/status/1940455920993198287</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-hindu-woman-kneeling-at-rath-yatra-in-puri-viral-with-false-claims-that-she-was-offering-namaz/</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:03:12.253099+00:00</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>पुरी में भगवान जगन्नाथ के रथ के नीच नमाज पढ़ी गई</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text itself makes the false claim that the viral video shows someone offering namaz in front of Jagannath's idol. However, fact-checker Alt News has debunked this claim by providing evidence from multiple sources including Khabardar Live and Odisha Police.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0953</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://twitter.com/MeghUpdates/status/1940432821014904911</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-hindu-woman-kneeling-at-rath-yatra-in-puri-viral-with-false-claims-that-she-was-offering-namaz/</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:03:12.255192+00:00</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The article debunks this specific viral video claiming Namaz was being performed and instead reveals it shows Hindu devotee sitting underneath the chariot during crowded festival; post's caption makes an unsubstantiated claim about Bangladeshis performing namaz under Rath of Jagannath.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0955</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>item-0042</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://twitter.com/erbmjha/status/1940447650127687683</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-hindu-woman-kneeling-at-rath-yatra-in-puri-viral-with-false-claims-that-she-was-offering-namaz/</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:03:14.236098+00:00</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): This classification choice comes from analyzing only this specific social media post and its text (caption). The article debunks the claim that a Hindu woman was offering namaz under Jagannath Rath in Puri as false. This particular X user (@erbmjha) shares the same viral video with similar claims, making it MISINFORMATION_SOURCE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0956</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://twitter.com/jpsin1/status/1940421871960494385</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-hindu-woman-kneeling-at-rath-yatra-in-puri-viral-with-false-claims-that-she-was-offering-namaz/</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:03:47.578980+00:00</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">जिस जगन्नाथ मंदिर में गैर-हिंदुओं का प्रवेश वर्जित है वहां एक मुस्लिम नमाज़ कैसे पढ़ रहा है, </t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=0.90): The post itself makes an unsubstantiated and misleading accusation about someone reading namaz at a place where non-Hindus are not allowed to enter. The article debunks the claim that she was offering prayers, providing evidence from multiple sources including Khabardar Live's Facebook page, Odisha Police officials, and people familiar with Islamic prayer practices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0957</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ocjain4/status/1940420687388393629</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-hindu-woman-kneeling-at-rath-yatra-in-puri-viral-with-false-claims-that-she-was-offering-namaz/</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:04:07.770873+00:00</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">पुरी में जगन्नाथ रथ के नीचे नमाज पढ़ रहे हैं </t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states the debunked claim that a woman was offering namaz under Jagannath Rath in Puri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0960</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://twitter.com/BJP4Goa/status/1941468480521502782</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/rahul-gandhis-photo-on-sanitary-pads-distributed-in-bihar-congress-files-fir-over-fake-video/</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:05:44.971413+00:00</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Bihar Congress distributing sanitary napkins attached with Rahul Gandhi’s images ‘at unwanted locations’.</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=0.90): The post's caption directly states the false claim made by BJP Goa and other pro-BJP users, which is debunked in the fact-check article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0961</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>item-0043</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://twitter.com/MrSinha_/status/1941444953080725842</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/rahul-gandhis-photo-on-sanitary-pads-distributed-in-bihar-congress-files-fir-over-fake-video/</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:05:44.975200+00:00</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Their hereditary habit of sucking blood.</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption directly states the false claim made by Rishi Bagree in his tweet, which is debunked by the fact-check article. The caption does not provide any additional context or clarify that it is a joke or satire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0962</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Pawankhera/status/1941512083146715196</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/rahul-gandhis-photo-on-sanitary-pads-distributed-in-bihar-congress-files-fir-over-fake-video/</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:05:44.978194+00:00</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Congress had attached Rahul Gandhi’s image ½ unwanted locations ahead of Bihar Elections</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0964</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=Vz6WErpV0Ec</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/rahul-gandhis-photo-on-sanitary-pads-distributed-in-bihar-congress-files-fir-over-fake-video/</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:05:44.986173+00:00</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Rahul Gandhi's picture is shown on a sanitary pad, which has infuriated the Congress.</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0965</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>item-0044</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://twitter.com/PoddarVaishali/status/1938818981927772411</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/false-claim-of-person-wearing-a-garland-of-slippers-in-bangladesh-is-hindu-teacher-fact-check/</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:07:14.813393+00:00</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>एक हिंदू शिक्षक ने 40 साल तक देश की सेवा की और बदले में बांग्लादेश में कुछ कट्टरपंथियों ने उन्हें चप्पलों की माला पहनाकर अपमानित किया। यह सिर्फ एक शिक्षक का नहीं, पूरे हिंदू समाज का अपमान है।</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states the debunked claim that a Hindu teacher was garlanded with shoes by Muslims in Bangladesh for making derogatory remarks about Prophet Mohammed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0987</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://twitter.com/iribnews_irib/status/1936422883774939247</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/identifying-an-impostor-verified-x-account-not-of-iranian-journalist-whose-show-was-interrupted-by-israeli-attacks/</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:13:45.460197+00:00</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption states that Sahar Emami does not have a Twitter page, and mentions an account with her name which was active but turned out to be fake. This statement is consistent with the article's claim about the impersonation of Iranian state TV anchor Sahar Emami on X (Twitter). The extracted claim from this post matches exactly what the fact-checking research debunks in its own text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0990</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zwB2rsiyJqE</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/identifying-an-impostor-verified-x-account-not-of-iranian-journalist-whose-show-was-interrupted-by-israeli-attacks/</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:13:48.618702+00:00</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Iranian state TV presenter Sahar Emami said moments before an Israeli missile struck the studio, halting her broadcast.</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption of this YouTube post is a direct quote from Al Jazeera's Dorsa Jabbari about Sahar Emami’s statement before an Israeli missile struck the studio, halting her broadcast. However, in another part of the article it was stated that “IRIB news shared a video on X and Instagram in which Sahar Emami clarifies that she has no X account.” This indicates that this YouTube post is actually quoting Al Jazeera's Dorsa Jabbari about what Iranian state TV presenter said before an Israeli missile struck her studio, NOT the actual quote from Sahar Emami. The original claim made by @iamSaharEmami on Twitter was false and has been debunked in the article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0991</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>item-0045</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>https://twitter.com/NavrtnYadav/status/1939360173342261413</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/dalit-man-tortured-in-jhansi-old-video-resurfaces-police-says-victim-assailants-from-same-community/</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:15:03.734204+00:00</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): Post states: 'ये तालिबानी सजा है भाजपा सरकार की कोई नहीं परिभाषा' (This is a Taliban-like punishment by BJP government). However, article debunks this claim stating that the victim and assailants are from same community. The post's caption also contains other false claims such as 'प्रभुत्ववादी लोगों के सरकार के संरक्षण में जो होसले' (those who get protected by powerful people in government) which is not supported by the article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0992</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>https://twitter.com/jhansipolice/status/1849885087980192007</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/dalit-man-tortured-in-jhansi-old-video-resurfaces-police-says-victim-assailants-from-same-community/</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:15:03.740802+00:00</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Now if a Yadav, Lodhi, or Dalit refuses to work as a labourer, their head is shaved, they are hung upside down and made to drink water, paraded through the entire village—this is the Taliban-like punishment of the BJP government.</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption states that 'their' head will be shaved if a Yadav or Lodhi refuses to work as laborer, but it does not specify Dalit. The article debunks the claim by stating that both parties are from the same community and there is no caste-based violence in this incident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0994</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>https://twitter.com/AlexDuncanTX/status/1938283614954750036</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-from-2023-pro-palestine-protest-viral-with-misleading-claims-that-muslims-are-ripping-us-flags-in-nyc/</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:35:43.816784+00:00</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Muslims tearing down American flags in NYC after Zohran Mamdani's electoral win</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): [The post states the claim that Muslims are taking down US flags in New York City 'after' a specific event (Zohran Mamdani's election), which is not supported by evidence from fact-check article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0996</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://twitter.com/RadioGenoa/status/1938116659526701288</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-from-2023-pro-palestine-protest-viral-with-misleading-claims-that-muslims-are-ripping-us-flags-in-nyc/</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:35:43.824976+00:00</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Muslims tearing down American flags in NYC after Zohran Mamdani's electoral win</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0997</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>https://twitter.com/coolfunnytshirt/status/1938457916794913127</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-from-2023-pro-palestine-protest-viral-with-misleading-claims-that-muslims-are-ripping-us-flags-in-nyc/</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:35:43.827414+00:00</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Muslims tearing down American flags in NYC after Zohran Mamdani's electoral win</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): [The post states the exact claim that is debunked by the article.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0998</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>item-0046</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>https://twitter.com/iAnonPatriot/status/1938295539113611452</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-from-2023-pro-palestine-protest-viral-with-misleading-claims-that-muslims-are-ripping-us-flags-in-nyc/</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:35:43.830335+00:00</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Muslims tearing down American flags in NYC after Zohran Mamdani's electoral win</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post’s caption states the debunked claim that Muslims are taking down US flags in New York City. The article provides evidence from a YouTube video uploaded on November 12, 2023, with a different context and description of events.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1004</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>item-0047</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>https://twitter.com/geetappoo/status/1936863809672786233</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/2021-video-from-delhis-yamuna-vihar-viral-with-misleading-claims-of-communal-disharmony/</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:38:07.793936+00:00</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">जनाब वहां लाउडस्पीकर बंद करवाने पहुंच गए और फिर हिन्दुओ ने बहुत शांति से इन शांतिदूतो को समझाया… </t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption states the exact same claim as mentioned in the viral video, which was debunked by fact-checkers to be misleading and false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1007</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Lawyer_Kalpana/status/1937942905957855690</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-husband-assaulting-wife-in-up-viral-with-false-communal-claims-that-muslim-man-beat-up-hindu-woman/</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:39:36.009295+00:00</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">देख लो सेक्युलर हिन्दू लड़कियों तुम्हारे साथ भी ऐसा ही होगा, अभी भी समय है घर वापसी करलो। </t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1011</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>https://twitter.com/virjust18/status/1935648360586707356</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-husband-assaulting-wife-in-up-viral-with-false-communal-claims-that-muslim-man-beat-up-hindu-woman/</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:39:37.941048+00:00</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>इस दरिंदे को क्या सजा मिलनी चाहिए ? *हापुड़ से बड़ी खबर हाथ जोड़ कर दया की भीख मांगती रही महिला व्यक्ति करता रहा पिटाई।*  हापुड़ में पति-पत्नी के रिश्ते को तार तार kar dena wala mामला सोशल मीडिया पर जमकर वायरल हो रहा है घर के अंदर महिला को pati bheramee se pita rahaa hai mahila haath joodkar</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1018</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=EPob-pLFC5g</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/digitally-manipulated-clip-of-abp-debate-shared-with-claims-that-iranian-lawmakers-burnt-indian-flag/</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:49:08.931254+00:00</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>ईरान के विदेश मंत्रालय पर इजरायल का हमला...इज़राइली हमलों में अब तक 14 वैज्ञानिक मारे गए...</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption mentions several claims about the Israeli attack on Iran, including that there were casualties and scientists killed. However, these are not supported by evidence in the article or other credible sources.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0021</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>item-0034</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>https://twitter.com/foxwoundband/status/1266613385862447104</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-atlanta-did-not-deploy-a-child-militia-during-protests.html</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:37:22.560671+00:00</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Atlanta has deployed a child militia at Lenox Mall fitted with riot shields and batons.</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states the debunked claim that Atlanta deployed 'a child militia' during recent protests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0437</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=J1OvDB_wavI</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-Kamala-Harris-did-not-call-Joe-Biden-a-racist-and-a-rapist.html</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:00:01.217068+00:00</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>1</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): The post's caption states: 'Sen. Kamala Harris of California blasts former Vice President Joe Biden for his previously held opinions on busing in schools.' This statement is false because it misrepresents what happened during their debate, where she criticized him but did not call him a racist or use the word </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0457</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6BEfZCH1nN8</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-annabelle-doll-did-not-escape-from-the-warren's-occult-museum.html</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:02:23.976555+00:00</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>1</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Annabelle doll escaped from The Warrens Occult Museum today 3.00 A.M.</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The claim that Annabelle the doll 'escaped' is stated in the post's own caption, which directly contradicts the debunked information provided by Tony Spera and other sources. The original article text explicitly states: "Annabelle did not escape..." This confirms that this Instagram post contains misinformation about the event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0460</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LFBYZ4rwjbw</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-cdc-did-not-predict-an-outbreak-of-afm-cases-to-cover-up-anticipated-future-vaccine-injuries.html</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:03:23.631057+00:00</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0469</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>https://twitter.com/livesmattershow/status/1295253759291879424</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-truck-driver-attacked-in-portland-near-black-lives-matter-protest-has-not-died.html</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:06:00.175987+00:00</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>The truck driver attacked in Portland has passed.</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): This post's own caption/text states the debunked claim that 'the man who was attacked on video during a protest' (has) "passed" which is false according to Lead Stories article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0503</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://twitter.com/DavidBrodyCBN/status/1296158619294146560</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-democrats-did-not-take-out-under-god-from-the-nightly-pledge-of-allegiance-at-their-national-convention.html</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:08:29.920219+00:00</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>1</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): [[The post's caption states the debunked claim that Democrats left out 'Under God' from their nightly Pledge of Allegiance at the Democratic National Convention, which is contradicted by fact-check article text]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0504</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://twitter.com/DavidBrodyCBN/status/1296164465432580099</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-democrats-did-not-take-out-under-god-from-the-nightly-pledge-of-allegiance-at-their-national-convention.html</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:08:29.923565+00:00</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>"Dems recited our beautiful pledge of allegiance tonight and took out 'UNDER GOD' !"}</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The Facebook screenshot shows videos embedded with each night's program including recitation of pledge where 'under god' was included in all four nights; The post claims that "Dems took out" words, but no such claim is made about Muslim Delegates Assembly or LGBT caucuses which are mentioned separately. Hence the caption itself makes a false statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0528</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>https://twitter.com/_SJPeace_/status/1298670510360928259</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-man-protecting-his-business-in-Kenosha-did-not-own-gas-station-where-he-allegedly-fired-at-protesters.html</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:10:41.760976+00:00</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>A 17 y/o white supremacist, Kyle Rittenhouse, drove from Illinois to Wisconsin w/ an AR-15 to TERRORIZE BLM PROTESTORS He shot several people ended up killing 2. Then is able to casually walk around police as if he didn't just murder! WHAT THE FUCK?!</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post contains several false claims, including the accusation that Rittenhouse was a white supremacist and drove to Kenosha with an intention to terrorize BLM protesters using an AR-15 (the actual weapon used by Kyle Rittenhouse resembled this rifle but it's called 'AR-style' semi-automatic). The caption also includes sensational language ('TERRORIZE', 'WHITE SUPREMACIST') that is not supported by evidence. In contrast, the fact-check article debunks these claims and provides context about Rittenhouse's background.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0537</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://twitter.com/CalebJHull/status/1298832317033705472</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-cnn-did-use-the-chyron-fiery-but-mostly-peaceful-protests-after-police-shooting.html</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:11:57.416994+00:00</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0554</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://twitter.com/TrumpWarRoom/status/1300495064838397952</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-war-room---text-trump-to-88022-on-twitter.html</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:15:01.730401+00:00</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>1</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>'You won't be safe in Joe Biden's America!'</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post itself states the exact phrase 'Joe Biden says "You won't be safe in Joe Biden's America!"' which matches exactly with what Trump campaign tweeted and misleadingly presented as a quote from Biden, making it MISINFORMATION_SOURCE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0573</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ProjectLincoln/status/1300905344693153796</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-did-not-say-americans-are-going-to-die-when-hes-not-president-in-doctored-lincoln-project-video.html</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:38:29.761925+00:00</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>going to die (when he isn't president)</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The article explicitly states that the Lincoln Project's video deceptively snipped footage from Trump's interview and took his words out of context. The actual quote is 'they're going to die' which refers to NBC ratings dying in five years when he isn't president.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0597</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UE_3LDvWcbY</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-video-does-not-show-portland-antifa-anarchist-camps-they-are-temporary-outdoor-homeless-shelters.html</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:49:46.109220+00:00</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>This encampment is filled with young vibrant people who are actively, at night, committing crimes...</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): [The narrator] says 'I'm not filming General homeless individuals.' This is a clear indication that he does not want people with general homelessness issues in the camp and instead focuses on young vibrant people who are actively committing crimes at night, which was later debunked by Denis Theriault as false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cand-mass-0027</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>item-0019</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DX7LBwesE-o/</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/bjp-media-outlets-share-holi-video-as-people-celebrating-bjp-victory-in-bengal/</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>candidates_v2.jsonl</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2026-08-18T00:59:01.077843+00:00</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>False claim: The post's own caption asserts that it depicts people celebrating a political event (BJP victory), but actually shows a pre-election celebration during Holi.</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Celebrations of Jai Sri Ram at the Holi celebrations in Kolkata, which took place two months before May 4th</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>llama3.2 judge (confidence=0.90): The Instagram Post’s Own Caption Asserts the False Claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cand-mass-0088</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DPcCJWxga06/</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/yogi-adityanath-left-to-hear-criticism-of-govt-while-ravi-kishan-was-enjoying-doctored-video-viral/</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>candidates_v2.jsonl</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2026-08-18T01:51:54.674020+00:00</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; REJECTED</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Judged NOT the misinformation source (confidence=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>cand-thequint-0182</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>item-0021</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>thequint.com</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DRmx_YwjN7Y/</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.thequint.com/news/webqoof/ai-generated-yogi-lifting-weighting-without-his-hands-fact-check</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>candidates_v2_mass_thequint.jsonl</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2026-08-18T05:29:58.023010+00:00</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>INDIAN YOGI MOVES 95 Kgs of weight in the gym with his mind!</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>llama3.2 judge (confidence=1.00): The caption text itself makes a specific false assertion about lifting '130 kgs' (not mentioned) and claims that it's done using one's 'mind', which is the exact same claim being debunked in the article.. NOT yet human/manual-reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>cand-vishvas-1173</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>item-0022</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>vishvasnews.com</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/C3tynQjr_wI/</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.vishvasnews.com/politics/fact-check-akhilesh-yadav-old-video-from-kanpur-is-being-shared-as-meeting-farmers-in-delhi/</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>candidates_v2_mass_vishvas.jsonl</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>2026-08-18T10:12:40.325601+00:00</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; ELIGIBLE -&gt; UNRESOLVED -&gt; ELIGIBLE</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>अखिलेश यादव किसानों से मिलने दिल्ली पहुंचे।</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>llama3.2 judge (confidence=1.00): The caption text itself makes the specific false assertion that 'अखिलेश यादव' is meeting with farmers in Delhi, which contradicts the fact-check article's conclusion.. NOT yet human/manual-reviewed.</t>
         </is>
@@ -9521,7 +14707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -9548,7 +14734,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07T15:38:20+00:00</t>
+          <t>2026-09-07T17:17:45+00:00</t>
         </is>
       </c>
     </row>
@@ -9559,7 +14745,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -9579,7 +14765,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6">
@@ -9621,46 +14807,46 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">    UNVERIFIED</t>
+          <t xml:space="preserve">    MISLEADING</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">    MISLEADING</t>
+          <t xml:space="preserve">    TRUE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">    TRUE</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
+          <t>--- platform distribution ---</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- platform distribution ---</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t xml:space="preserve">    x</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9675,143 +14861,143 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    x</t>
+          <t xml:space="preserve">    (none)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
+          <t xml:space="preserve">    facebook</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">    facebook</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
+          <t>--- language distribution ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>--- language distribution ---</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t xml:space="preserve">    en</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    en</t>
+          <t xml:space="preserve">    hi</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">    hi</t>
+          <t xml:space="preserve">    hi-en-mixed</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">    hi-en-mixed</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
+          <t>--- split distribution ---</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- split distribution ---</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t xml:space="preserve">    validation</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    validation</t>
+          <t xml:space="preserve">    (none)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>9</v>
-      </c>
+          <t>--- benchmark_version distribution ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- benchmark_version distribution ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t xml:space="preserve">    v2</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    v2</t>
+          <t xml:space="preserve">    v1</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">    v1</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>9</v>
-      </c>
+          <t>--- claim_type distribution ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>--- claim_type distribution ---</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t xml:space="preserve">    provenance</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>40</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    provenance</t>
+          <t xml:space="preserve">    event</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -9837,7 +15023,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    event</t>
+          <t xml:space="preserve">    quote</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -9847,73 +15033,73 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">    quote</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
+          <t>--- media (video/photo) distribution ---</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>--- media (video/photo) distribution ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t xml:space="preserve">    video</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>44</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    video</t>
+          <t xml:space="preserve">    photo</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">    photo</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>3</v>
-      </c>
+          <t>--- factchecker distribution ---</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>--- factchecker distribution ---</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t xml:space="preserve">    altnews.in</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    altnews.in</t>
+          <t xml:space="preserve">    boomlive.in</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">    boomlive.in</t>
+          <t xml:space="preserve">    tier-1-source:boomlive.in</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:boomlive.in</t>
+          <t xml:space="preserve">    tier-1-source:altnews.in</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -9923,17 +15109,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:altnews.in</t>
+          <t xml:space="preserve">    tier-1-source:factly.in</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:factly.in</t>
+          <t xml:space="preserve">    tier-1-source:boomlive.in (hindi.boomlive.in)</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -9943,7 +15129,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:boomlive.in (hindi.boomlive.in)</t>
+          <t xml:space="preserve">    tier-1-source:altnews.in (hindi.altnews.in)</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -9953,7 +15139,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:altnews.in (hindi.altnews.in)</t>
+          <t xml:space="preserve">    thequint.com</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -9963,7 +15149,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    thequint.com</t>
+          <t xml:space="preserve">    vishvasnews.com</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -9973,7 +15159,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    vishvasnews.com</t>
+          <t xml:space="preserve">    leadstories.com</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -9983,75 +15169,75 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">    leadstories.com</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
+          <t>--- ground-truth tier distribution ---</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>--- ground-truth tier distribution ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t xml:space="preserve">    (none)</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
+          <t xml:space="preserve">    1</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>9</v>
-      </c>
+          <t>--- difficulty distribution ---</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>--- difficulty distribution ---</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t xml:space="preserve">    (none)</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>34</v>
-      </c>
+          <t>--- annotation_status distribution ---</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>--- annotation_status distribution ---</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
+          <t xml:space="preserve">    (none)</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
+          <t xml:space="preserve">    reviewed</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56">
@@ -10067,156 +15253,166 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>--- modality availability (true count) ---</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t xml:space="preserve">    needs_review</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">    audio_available</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>19</v>
-      </c>
+          <t>--- modality availability (true count) ---</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ocr_available</t>
+          <t xml:space="preserve">    audio_available</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    caption_available</t>
+          <t xml:space="preserve">    ocr_available</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    visual_information_available</t>
+          <t xml:space="preserve">    caption_available</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>--- cross-post ---</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr"/>
+          <t xml:space="preserve">    visual_information_available</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">    cross_post_possible = true</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>25</v>
-      </c>
+          <t>--- cross-post ---</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">    cross_post_verified = true</t>
+          <t xml:space="preserve">    cross_post_possible = true</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>--- missing-field rates ---</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr"/>
+          <t xml:space="preserve">    cross_post_verified = true</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no factcheck_url</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>0/34 (0%)</t>
-        </is>
-      </c>
+          <t>--- missing-field rates ---</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no publication_date</t>
+          <t xml:space="preserve">    no factcheck_url</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>25/34 (73%)</t>
+          <t>0/47 (0%)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no media_hash</t>
+          <t xml:space="preserve">    no publication_date</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>9/34 (26%)</t>
+          <t>38/47 (80%)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no split</t>
+          <t xml:space="preserve">    no media_hash</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9/34 (26%)</t>
+          <t>9/47 (19%)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no difficulty</t>
+          <t xml:space="preserve">    no split</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>34/34 (100%)</t>
+          <t>9/47 (19%)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t xml:space="preserve">    no difficulty</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>47/47 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t xml:space="preserve">    no candidate_id (provenance)</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>9/34 (26%)</t>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>9/47 (19%)</t>
         </is>
       </c>
     </row>
@@ -12360,7 +17556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -12408,17 +17604,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61a7ad6</t>
+          <t>a97658e</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Promote item-0022; fix malformed labels on 2 already-promoted items</t>
+          <t>Review-gated promotion batches 1-2: +10 human-reviewed items (BENCHMARK 42-&gt;47)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -12426,17 +17622,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>764c446</t>
+          <t>69c0ca1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Promote item-0021 from WebQoof; harden spot-check + merge locking</t>
+          <t>Checkpoint before switching to review-gated promotion (BENCHMARK=37)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -12444,17 +17640,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>a67aad9</t>
+          <t>6b2ed7b</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fix real concurrent-write data loss that crashed the Alt News pipeline</t>
+          <t>Dataset checkpoint: 34 benchmark items (was 22); +12 promoted from all-platform sourcing this session</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -12467,12 +17663,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>cdfde33</t>
+          <t>61a7ad6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Promote item-0018: AI-generated protest-death fabrication (benchmark: 17 -&gt; 18)</t>
+          <t>Promote item-0022; fix malformed labels on 2 already-promoted items</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -12485,12 +17681,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>b1c577c</t>
+          <t>764c446</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Promote item-0017: second AI-generated-image case (benchmark: 16 -&gt; 17)</t>
+          <t>Promote item-0021 from WebQoof; harden spot-check + merge locking</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -12503,12 +17699,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1bc264e</t>
+          <t>a67aad9</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fix embed-widget sourcing gap, promote item-0016 (benchmark: 15 -&gt; 16)</t>
+          <t>Fix real concurrent-write data loss that crashed the Alt News pipeline</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -12516,17 +17712,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6773a7f</t>
+          <t>cdfde33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Promote all 6 ELIGIBLE v2 candidates via real ingestion (items 0010-0015)</t>
+          <t>Promote item-0018: AI-generated protest-death fabrication (benchmark: 17 -&gt; 18)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -12534,17 +17730,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9d0a591</t>
+          <t>b1c577c</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dataset pass 3: 2 more Tier-1 items, first quote-type claim, real misses logged</t>
+          <t>Promote item-0017: second AI-generated-image case (benchmark: 16 -&gt; 17)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -12552,17 +17748,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1767254</t>
+          <t>1bc264e</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Day 2 pass 2: 2 more Tier-1 items, closing claim-type and language gaps</t>
+          <t>Fix embed-widget sourcing gap, promote item-0016 (benchmark: 15 -&gt; 16)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -12570,20 +17766,74 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>6773a7f</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Promote all 6 ELIGIBLE v2 candidates via real ingestion (items 0010-0015)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>9d0a591</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dataset pass 3: 2 more Tier-1 items, first quote-type claim, real misses logged</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1767254</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Day 2 pass 2: 2 more Tier-1 items, closing claim-type and language gaps</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>fbacfb9</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Day 2: held-out dataset now at 5 real Tier-1 items (up from 2), plus annotation protocol</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/research/dataset/TruthLens_Dataset.xlsx
+++ b/research/dataset/TruthLens_Dataset.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07T17:17:45+00:00</t>
+          <t>2026-09-07T18:34:47+00:00</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a97658e</t>
+          <t>172b21b</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AK57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -6176,6 +6176,1116 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>item-0048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1007</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Lawyer_Kalpana/status/1937942905957855690</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-husband-assaulting-wife-in-up-viral-with-false-communal-claims-that-muslim-man-beat-up-hindu-woman/</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>A viral video of a man brutally assaulting a woman shows a Muslim man beating his Hindu wife, illustrating the fate that awaits Hindu women who marry Muslim men.</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Alt News: the clip is a domestic-violence incident and the communal 'Muslim man beat up Hindu woman' framing is false (article title: '...viral with false communal claims that Muslim man beat up Hindu woman').</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-husband-assaulting-wife-in-up-viral-with-false-communal-claims-that-muslim-man-beat-up-hindu-woman/</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W49" t="b">
+        <v>1</v>
+      </c>
+      <c r="X49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD49" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>e065197948a1ee30e443a9e570910d28fd78096811c3823d4a6a07c7ed81cb63</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:39:36.009295+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>item-0049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0469</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>https://twitter.com/livesmattershow/status/1295253759291879424</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-truck-driver-attacked-in-portland-near-black-lives-matter-protest-has-not-died.html</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>The truck driver who was dragged from his pickup and beaten near a Black Lives Matter protest in Portland, Oregon has died.</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Lead Stories: Portland police confirmed on Aug 18, 2020 that the victim had not died and had been released from the hospital and was recovering.</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-truck-driver-attacked-in-portland-near-black-lives-matter-protest-has-not-died.html</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="W50" t="b">
+        <v>1</v>
+      </c>
+      <c r="X50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD50" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>d684192c3a513dacb5fefd9a3c941f9c0a853a1edebc1b7599dda5be3ab1ab61</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:06:00.175987+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>item-0050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0504</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>https://twitter.com/DavidBrodyCBN/status/1296164465432580099</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-democrats-did-not-take-out-under-god-from-the-nightly-pledge-of-allegiance-at-their-national-convention.html</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Democratic Party</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Democrats removed the words 'under God' from the Pledge of Allegiance when it was recited during the 2020 Democratic National Convention.</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Lead Stories: 'Under God' was included in the Pledge on all four nights of the DNC's prime-time events; embedded convention video confirms this.</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-democrats-did-not-take-out-under-god-from-the-nightly-pledge-of-allegiance-at-their-national-convention.html</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="W51" t="b">
+        <v>1</v>
+      </c>
+      <c r="X51" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD51" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>b3eee4b23ba42b6fad7997928fc946755ddef491bd44d30b3530acf0b302e06e</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:08:29.923565+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>item-0051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0537</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>https://twitter.com/CalebJHull/status/1298832317033705472</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-cnn-did-use-the-chyron-fiery-but-mostly-peaceful-protests-after-police-shooting.html</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>CNN</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>CNN displayed the on-screen caption 'FIERY BUT MOSTLY PEACEFUL PROTESTS AFTER POLICE SHOOTING' over live video of a building engulfed in flames during the Kenosha, Wisconsin protests.</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Lead Stories: 'Yes, this is true' -- CNN used that chyron in an Aug 25, 2020 live report from Kenosha; the footage was not photoshopped or fake.</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-cnn-did-use-the-chyron-fiery-but-mostly-peaceful-protests-after-police-shooting.html</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="W52" t="b">
+        <v>1</v>
+      </c>
+      <c r="X52" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y52" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD52" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>c20a6e25d2d29956f648b3c6f188c68bc389e286bdf9edec44250d46ddb622a4</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:11:57.416994+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>item-0052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0554</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>https://twitter.com/TrumpWarRoom/status/1300495064838397952</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-war-room---text-trump-to-88022-on-twitter.html</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Joe Biden</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Joe Biden said 'You won't be safe in Joe Biden's America.'</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Lead Stories: Biden was quoting the Trump campaign's / Mike Pence's attack line and immediately rebutted it; the Trump War Room clip omits the opening of the sentence to reverse its meaning.</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-war-room---text-trump-to-88022-on-twitter.html</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="W53" t="b">
+        <v>1</v>
+      </c>
+      <c r="X53" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD53" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>09e24bc4817c1d1ae652cead7b533d64b2a96fbbc559bc3671af3f05d222e8ee</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:15:01.730401+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>item-0053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0573</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ProjectLincoln/status/1300905344693153796</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-did-not-say-americans-are-going-to-die-when-hes-not-president-in-doctored-lincoln-project-video.html</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Donald Trump</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>In a video, President Donald Trump says Americans are 'going to die' when he is no longer president and calls his own campaign staff 'incompetent and stupid.'</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Lead Stories: The Lincoln Project ad deceptively snipped out-of-context clips from Trump's Aug 31, 2020 Fox News interview with Laura Ingraham; the quotes do not reflect what he actually said.</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-did-not-say-americans-are-going-to-die-when-hes-not-president-in-doctored-lincoln-project-video.html</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="W54" t="b">
+        <v>1</v>
+      </c>
+      <c r="X54" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y54" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD54" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>da43abd780e97397306a4c879cecb5eb7dde62b12ee5bee08f92dc720b74de62</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:38:29.761925+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>item-0054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0908</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>https://twitter.com/mRupeshVerma/status/1942534356423315824</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/claim-that-india-has-invented-a-self-sustaining-generator-that-runs-for-700-years-without-power-fuel-is-fabricated/</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>BJP</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>India, under the Narendra Modi government, has invented a self-sustaining magnetic power generator that runs for 700 years without any fuel or external power supply.</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Alt News: the claim is fabricated -- no such invention exists (article title: 'Claim that India has invented a self-sustaining generator that runs for 700 years without power/fuel is fabricated').</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/claim-that-india-has-invented-a-self-sustaining-generator-that-runs-for-700-years-without-power-fuel-is-fabricated/</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+      <c r="W55" t="b">
+        <v>1</v>
+      </c>
+      <c r="X55" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD55" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>abc6103e77cd3550c25e22871e401cbb8d4a0c49bdefa67a2db4893c149cec06</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:53:59.715900+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>item-0055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0887</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>https://twitter.com/vinushareddyb/status/1947659232813387834</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/poor-should-remain-poor-bengal-bjp-shares-clipped-video-distorting-context-of-mamatas-2024-martyrs-day-remarks/</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Mamata Banerjee</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>West Bengal Chief Minister Mamata Banerjee said in a speech that she wants the people of Bengal to remain poor and survive on whatever food they have at home.</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Alt News: Bengal BJP shared a ~8-second clipped video that distorts the context of Banerjee's July 21, 2024 Martyrs' Day remarks (article title: '...Bengal BJP shares clipped video distorting context of Mamata's 2024 Martyrs' Day remarks').</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/poor-should-remain-poor-bengal-bjp-shares-clipped-video-distorting-context-of-mamatas-2024-martyrs-day-remarks/</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="W56" t="b">
+        <v>1</v>
+      </c>
+      <c r="X56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD56" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>516ef5462b151d1194079b5df8352bc2a05b6fba382e7ceb77f866f06dceee17</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:49:21.302808+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>item-0056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-0898</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/707531534863299</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/screenshots-from-a-scripted-video-shared-with-false-claim-that-72-years-old-man-married-21-years-old-girl/</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Photographs show a real incident in which a 72-year-old man married a 21-year-old girl whom he had adopted and raised since childhood.</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Alt News: the images are screenshots from a scripted video, not a real incident (article title: 'Screenshots from a scripted video shared with false claim that 72-years-old man married 21-years-old girl').</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/screenshots-from-a-scripted-video-shared-with-false-claim-that-72-years-old-man-married-21-years-old-girl/</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W57" t="b">
+        <v>1</v>
+      </c>
+      <c r="X57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD57" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>942204b257d93fd610943fca226685c74eb4dbb7f4ae6a91667de13b626b4df1</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-07</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>2026-09-07T15:52:49.794402+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6187,7 +7297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9233,6 +10343,249 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>item-0048</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>A viral video of a man brutally assaulting a woman shows a Muslim man beating his Hindu wife, illustrating the fate that awaits Hindu women who marry Muslim men.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>item-0049</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>The truck driver who was dragged from his pickup and beaten near a Black Lives Matter protest in Portland, Oregon has died.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>item-0050</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Democrats removed the words 'under God' from the Pledge of Allegiance when it was recited during the 2020 Democratic National Convention.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>item-0051</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CNN displayed the on-screen caption 'FIERY BUT MOSTLY PEACEFUL PROTESTS AFTER POLICE SHOOTING' over live video of a building engulfed in flames during the Kenosha, Wisconsin protests.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>item-0052</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Joe Biden said 'You won't be safe in Joe Biden's America.'</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>item-0053</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>In a video, President Donald Trump says Americans are 'going to die' when he is no longer president and calls his own campaign staff 'incompetent and stupid.'</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>item-0054</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>India, under the Narendra Modi government, has invented a self-sustaining magnetic power generator that runs for 700 years without any fuel or external power supply.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>event</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>item-0055</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>West Bengal Chief Minister Mamata Banerjee said in a speech that she wants the people of Bengal to remain poor and survive on whatever food they have at home.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>item-0056</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Photographs show a real incident in which a 72-year-old man married a 21-year-old girl whom he had adopted and raised since childhood.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9244,7 +10597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -11090,6 +12443,11 @@
           <t>cand-ap-altnews-0887</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>item-0055</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -11155,6 +12513,11 @@
           <t>cand-ap-altnews-0898</t>
         </is>
       </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>item-0056</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -11216,6 +12579,11 @@
           <t>cand-ap-altnews-0908</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>item-0054</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -13504,6 +14872,11 @@
           <t>cand-ap-altnews-1007</t>
         </is>
       </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>item-0048</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -13696,12 +15069,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0021</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>item-0034</t>
+          <t>cand-ap-altnews-1023</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -13711,32 +15079,32 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://twitter.com/foxwoundband/status/1266613385862447104</t>
+          <t>https://www.youtube.com/watch?v=DaCTKi_wXJU</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-atlanta-did-not-deploy-a-child-militia-during-protests.html</t>
+          <t>https://www.altnews.in/viral-image-does-not-show-70-year-old-muslim-man-from-rajasthan-married-to-his-teen-granddaughter/</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-09-07T14:37:22.560671+00:00</t>
+          <t>2026-09-07T17:59:32.663994+00:00</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -13745,7 +15113,7 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -13754,19 +15122,19 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Atlanta has deployed a child militia at Lenox Mall fitted with riot shields and batons.</t>
+          <t>राजस्थान के चूरू में 70 साल के लियाकत अली ने अपनी 19साल की पोती के साथ में शादी कर ली है। माता-पिता के गुजरने के बाद लियाकत ने हीं अपनी पोती की परवरिश की थी। लेकिन जवान होने के बाद उनकी पोती खूबसूरत लगने लगी। जिसके बाद लियाक्त अली का मन मचल गया और उन्होंने अपनी पोती के साथ शादी कर ली।</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The post's own caption/text states the debunked claim that Atlanta deployed 'a child militia' during recent protests.</t>
+          <t>llama3.2 (conf=0.99): The claim made in the caption is identical to what was debunked by fact-checker Alt News, which states that Liaquat Ali and Shumaila Ali are not related and their marriage story does not involve a granddaughter.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0437</t>
+          <t>cand-ap-altnews-1024</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -13776,32 +15144,32 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=J1OvDB_wavI</t>
+          <t>https://twitter.com/AmitSingh0208/status/1935284059141267895</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-Kamala-Harris-did-not-call-Joe-Biden-a-racist-and-a-rapist.html</t>
+          <t>https://www.altnews.in/clip-of-air-india-crash-survivor-vishwas-kumar-ramesh-going-back-to-look-for-brother-viral-with-conspiracy-theories/</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-09-07T16:00:01.217068+00:00</t>
+          <t>2026-09-07T18:00:00.577698+00:00</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -13820,14 +15188,14 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t xml:space="preserve">llama3.2 (conf=1.00): The post's caption states: 'Sen. Kamala Harris of California blasts former Vice President Joe Biden for his previously held opinions on busing in schools.' This statement is false because it misrepresents what happened during their debate, where she criticized him but did not call him a racist or use the word </t>
+          <t>llama3.2 (conf=1.00): The X post's own caption/text states the false claim that Vishwas Kumar Ramesh was found walking inside the accident zone area and then again came out, which is contrary to what fact-check article debunks about his actions.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0457</t>
+          <t>cand-ap-altnews-1025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -13837,32 +15205,32 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=6BEfZCH1nN8</t>
+          <t>https://twitter.com/PTI_News/status/1934625235149697385</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-annabelle-doll-did-not-escape-from-the-warren's-occult-museum.html</t>
+          <t>https://www.altnews.in/clip-of-air-india-crash-survivor-vishwas-kumar-ramesh-going-back-to-look-for-brother-viral-with-conspiracy-theories/</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-09-07T16:02:23.976555+00:00</t>
+          <t>2026-09-07T18:00:00.585115+00:00</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -13871,28 +15239,24 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Annabelle doll escaped from The Warrens Occult Museum today 3.00 A.M.</t>
-        </is>
-      </c>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The claim that Annabelle the doll 'escaped' is stated in the post's own caption, which directly contradicts the debunked information provided by Tony Spera and other sources. The original article text explicitly states: "Annabelle did not escape..." This confirms that this Instagram post contains misinformation about the event.</t>
+          <t>llama3.2 (conf=0.90): The post's caption states that Ramesh walked into a building gate as plumes of smoke could be seen in the background, which is different from what was shown on social media (the viral video shows him walking towards the site of the crash). The article debunks this claim by stating he actually entered and exited through an emergency exit. This caption makes the false claim that Ramesh walked into a building gate as plumes of smoke could be seen in the background, which is not supported by evidence.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0460</t>
+          <t>cand-ap-altnews-1026</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -13902,32 +15266,32 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=LFBYZ4rwjbw</t>
+          <t>https://twitter.com/lordshivom/status/1935365138493882751</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-cdc-did-not-predict-an-outbreak-of-afm-cases-to-cover-up-anticipated-future-vaccine-injuries.html</t>
+          <t>https://www.altnews.in/clip-of-air-india-crash-survivor-vishwas-kumar-ramesh-going-back-to-look-for-brother-viral-with-conspiracy-theories/</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-09-07T16:03:23.631057+00:00</t>
+          <t>2026-09-07T18:00:00.591391+00:00</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -13936,24 +15300,28 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>does this viral video show Vishwas Kumar Ramesh entering and exiting a crash site in an unusual manner?</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+          <t>llama3.2 (conf=0.80): The post's caption does not directly state the debunked claim but asks readers to 'reconsider carefully'. This could be interpreted as questioning official narratives, which is different from stating or implying that Vishwas Kumar Ramesh entered and exited a crash site in an unusual manner.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0469</t>
+          <t>cand-ap-altnews-1027</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -13963,32 +15331,32 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://twitter.com/livesmattershow/status/1295253759291879424</t>
+          <t>https://www.youtube.com/watch?v=YgFi1ES_-HM</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-truck-driver-attacked-in-portland-near-black-lives-matter-protest-has-not-died.html</t>
+          <t>https://www.altnews.in/clip-of-air-india-crash-survivor-vishwas-kumar-ramesh-going-back-to-look-for-brother-viral-with-conspiracy-theories/</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-09-07T16:06:00.175987+00:00</t>
+          <t>2026-09-07T18:00:00.606258+00:00</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -14001,24 +15369,24 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>The truck driver attacked in Portland has passed.</t>
+          <t>He kept going in and out of the complex. We told him to stop, and dragged him away to an ambulance so that he could receive medical care… That’s when he said to me that his relative was trapped inside and he wanted to go save him.</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): This post's own caption/text states the debunked claim that 'the man who was attacked on video during a protest' (has) "passed" which is false according to Lead Stories article.</t>
+          <t>llama3.2 (conf=1.00): The caption of the YouTube post states a claim about Vishwas Kumar Ramesh's actions at the crash site, which is contradicted by evidence from other sources. Specifically, it claims that he 'kept going in and out' without permission, while actual reports suggest this was not true: according to Satinder Singh Sandhu (the first emergency responder), they told him to stop trying to go back into the complex because his relative had already been rescued.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0503</t>
+          <t>cand-ap-altnews-1031</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -14028,32 +15396,32 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>youtube</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://twitter.com/DavidBrodyCBN/status/1296158619294146560</t>
+          <t>https://www.youtube.com/watch?v=gT9iN3qRAGw</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-democrats-did-not-take-out-under-god-from-the-nightly-pledge-of-allegiance-at-their-national-convention.html</t>
+          <t>https://www.altnews.in/viral-image-does-not-show-xi-jinpings-daughter-news-outlets-photo-agencies-getty-alamy-misidentify-xi-mingze/</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-09-07T16:08:29.920219+00:00</t>
+          <t>2026-09-07T18:01:19.600717+00:00</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -14072,14 +15440,14 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): [[The post's caption states the debunked claim that Democrats left out 'Under God' from their nightly Pledge of Allegiance at the Democratic National Convention, which is contradicted by fact-check article text]]</t>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0504</t>
+          <t>cand-ap-altnews-1033</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -14089,7 +15457,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -14099,22 +15467,22 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://twitter.com/DavidBrodyCBN/status/1296164465432580099</t>
+          <t>https://twitter.com/LibTearCreator1/status/1935287632595947638</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-democrats-did-not-take-out-under-god-from-the-nightly-pledge-of-allegiance-at-their-national-convention.html</t>
+          <t>https://www.altnews.in/video-of-iranian-women-protesting-mahsa-aminis-custodial-killing-in-2022-linked-to-june-conflict-with-israel/</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-09-07T16:08:29.923565+00:00</t>
+          <t>2026-09-07T18:02:17.551761+00:00</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -14130,21 +15498,17 @@
           <t>FALSE</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>"Dems recited our beautiful pledge of allegiance tonight and took out 'UNDER GOD' !"}</t>
-        </is>
-      </c>
+      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The Facebook screenshot shows videos embedded with each night's program including recitation of pledge where 'under god' was included in all four nights; The post claims that "Dems took out" words, but no such claim is made about Muslim Delegates Assembly or LGBT caucuses which are mentioned separately. Hence the caption itself makes a false statement.</t>
+          <t>llama3.2 (conf=1.00):  The original text states: &amp;quot;To verify the authenticity of the claims, we ran a reverse image search on one of the key frames from the viral video... This led us to an X post, from October 5, 2022, which features the same clip that has recently gone viral. ... Students in various schools and universities across Iran flouted the strict moral codes by refusing to cover their heads, to protest the custodial killing of Mahsa Amini.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0528</t>
+          <t>cand-ap-altnews-1034</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -14154,7 +15518,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -14164,22 +15528,22 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://twitter.com/_SJPeace_/status/1298670510360928259</t>
+          <t>https://twitter.com/PankajTiwarri/status/1935246813235138906</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-man-protecting-his-business-in-Kenosha-did-not-own-gas-station-where-he-allegedly-fired-at-protesters.html</t>
+          <t>https://www.altnews.in/video-of-iranian-women-protesting-mahsa-aminis-custodial-killing-in-2022-linked-to-june-conflict-with-israel/</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-09-07T16:10:41.760976+00:00</t>
+          <t>2026-09-07T18:02:17.556224+00:00</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -14188,28 +15552,24 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>A 17 y/o white supremacist, Kyle Rittenhouse, drove from Illinois to Wisconsin w/ an AR-15 to TERRORIZE BLM PROTESTORS He shot several people ended up killing 2. Then is able to casually walk around police as if he didn't just murder! WHAT THE FUCK?!</t>
-        </is>
-      </c>
+      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The post contains several false claims, including the accusation that Rittenhouse was a white supremacist and drove to Kenosha with an intention to terrorize BLM protesters using an AR-15 (the actual weapon used by Kyle Rittenhouse resembled this rifle but it's called 'AR-style' semi-automatic). The caption also includes sensational language ('TERRORIZE', 'WHITE SUPREMACIST') that is not supported by evidence. In contrast, the fact-check article debunks these claims and provides context about Rittenhouse's background.</t>
+          <t>llama3.2 (conf=1.00): The original text explicitly debunks this claim as misleading; it was taken from October 2022 protests following Mahsa Amini's custodial killing in September. The post is sharing a video that has been previously debunked by fact-checkers and news outlets.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0537</t>
+          <t>cand-ap-altnews-1036</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -14219,7 +15579,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -14229,22 +15589,22 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://twitter.com/CalebJHull/status/1298832317033705472</t>
+          <t>https://twitter.com/journorai/status/1935234293569392987</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-cnn-did-use-the-chyron-fiery-but-mostly-peaceful-protests-after-police-shooting.html</t>
+          <t>https://www.altnews.in/video-of-iranian-women-protesting-mahsa-aminis-custodial-killing-in-2022-linked-to-june-conflict-with-israel/</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-09-07T16:11:57.416994+00:00</t>
+          <t>2026-09-07T18:02:17.570873+00:00</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -14253,24 +15613,28 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr"/>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Iranian girls remove their hijabs, take over their school, and chant “Death to the dictator and the Islamic regime.” https://t.co/5BBySndLkH </t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+          <t>llama3.2 (conf=1.00): The caption of this post states the exact same claim that is debunked in the fact-check article, which was also made by other users (@realMaalouf and @sumit45678901). The only difference being a slight variation with an additional hashtag (#IranVsIsrael) but not altering its meaning. This confirms it as MISINFORMATION_SOURCE.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0554</t>
+          <t>cand-ap-altnews-1038</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -14280,7 +15644,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -14290,22 +15654,22 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://twitter.com/TrumpWarRoom/status/1300495064838397952</t>
+          <t>https://twitter.com/realMaalouf/status/1935182415124660459</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-war-room---text-trump-to-88022-on-twitter.html</t>
+          <t>https://www.altnews.in/video-of-iranian-women-protesting-mahsa-aminis-custodial-killing-in-2022-linked-to-june-conflict-with-israel/</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-09-07T16:15:01.730401+00:00</t>
+          <t>2026-09-07T18:02:26.691128+00:00</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -14318,24 +15682,24 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>'You won't be safe in Joe Biden's America!'</t>
+          <t>chanted 'Death to the dictator and the Islamic regime'</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The post itself states the exact phrase 'Joe Biden says "You won't be safe in Joe Biden's America!"' which matches exactly with what Trump campaign tweeted and misleadingly presented as a quote from Biden, making it MISINFORMATION_SOURCE.</t>
+          <t>llama3.2 (conf=1.00): This post's caption directly states that Iranian girls remove their hijabs, take over their school, and chant “Death to the dictator and the Islamic regime”. This claim is debunked by the fact-check article as being unrelated to the June conflict with Israel.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0573</t>
+          <t>cand-ap-altnews-1042</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -14345,32 +15709,32 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://twitter.com/ProjectLincoln/status/1300905344693153796</t>
+          <t>https://www.facebook.com/sajalghoshofc/videos/1255513172727328</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-did-not-say-americans-are-going-to-die-when-hes-not-president-in-doctored-lincoln-project-video.html</t>
+          <t>https://www.altnews.in/waterlogged-kolkata-street-did-turn-red-after-eid-qurbani-alt-news-ground-report-rebuts-police-cyber-cells-denial/</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-09-07T16:38:29.761925+00:00</t>
+          <t>2026-09-07T18:03:29.881226+00:00</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -14383,24 +15747,24 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>going to die (when he isn't president)</t>
+          <t>\n\na ઩ \u09e4 \u098f \u0995 \u0968 \u097b \u093c \u094d, \u0ba3 \u0926 \u0902 \u0917 \u0931 \u093f \u095a\n\nei ࣮ \u09e4 \u0989 \u0995 \u0968 \u097b \u093c \u094d, \u0ba3 \u0926 \u0902</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): The article explicitly states that the Lincoln Project's video deceptively snipped footage from Trump's interview and took his words out of context. The actual quote is 'they're going to die' which refers to NBC ratings dying in five years when he isn't president.</t>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states the false claim that parts of Kolkata resemble 'scenes from Bangladesh' and claims it is from Ward No. 50 in the KMC (Kolkata Municipal Corporation), which matches Sajal Ghosh’s Facebook post, but has been debunked by fact-checking sources as originating from a different location.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>cand-ap-leadstories-0597</t>
+          <t>cand-ap-altnews-1043</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -14410,32 +15774,32 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>leadstories.com</t>
+          <t>altnews.in</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>youtube</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/watch?v=UE_3LDvWcbY</t>
+          <t>https://www.facebook.com/watch/?v=1006771171539811</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-video-does-not-show-portland-antifa-anarchist-camps-they-are-temporary-outdoor-homeless-shelters.html</t>
+          <t>https://www.altnews.in/waterlogged-kolkata-street-did-turn-red-after-eid-qurbani-alt-news-ground-report-rebuts-police-cyber-cells-denial/</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>candidates_v3_leadstories.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-09-07T16:49:46.109220+00:00</t>
+          <t>2026-09-07T18:03:29.884830+00:00</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -14444,33 +15808,28 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>This encampment is filled with young vibrant people who are actively, at night, committing crimes...</t>
+          <t>এটা বাংলাদেশ না। এটা পাকিস্তানও না৷</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>llama3.2 (conf=1.00): [The narrator] says 'I'm not filming General homeless individuals.' This is a clear indication that he does not want people with general homelessness issues in the camp and instead focuses on young vibrant people who are actively committing crimes at night, which was later debunked by Denis Theriault as false.</t>
+          <t>llama3.2 (conf=0.90): The caption explicitly claims that the photo was taken neither in Bangladesh nor in Pakistan.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>cand-mass-0027</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>item-0019</t>
+          <t>cand-ap-altnews-1044</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -14483,56 +15842,64 @@
           <t>altnews.in</t>
         </is>
       </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DX7LBwesE-o/</t>
+          <t>https://www.facebook.com/watch/?v=718811544639473</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.altnews.in/bjp-media-outlets-share-holi-video-as-people-celebrating-bjp-victory-in-bengal/</t>
+          <t>https://www.altnews.in/waterlogged-kolkata-street-did-turn-red-after-eid-qurbani-alt-news-ground-report-rebuts-police-cyber-cells-denial/</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>candidates_v2.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-08-18T00:59:01.077843+00:00</t>
+          <t>2026-09-07T18:03:29.894308+00:00</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
-        </is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>1</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>False claim: The post's own caption asserts that it depicts people celebrating a political event (BJP victory), but actually shows a pre-election celebration during Holi.</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Celebrations of Jai Sri Ram at the Holi celebrations in Kolkata, which took place two months before May 4th</t>
+          <t>\u0ba8\u09ac \u0999\u093f ঄\u094d\u092e \u0902\u0917\u0966\u097b\u0951\u093c\u094a</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>llama3.2 judge (confidence=0.90): The Instagram Post’s Own Caption Asserts the False Claim</t>
+          <t>llama3.2 (conf=1.00): The post claims that the video is from Ward No. 44 in Kolkata Municipal Corporation (KMC), but according to the fact-check article, it was actually filmed on Bhawani Dutta Lane and Neel Madhab Sen Lane areas of Bowbazar.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>cand-mass-0088</t>
+          <t>cand-ap-altnews-1045</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>REJECTED</t>
+          <t>ELIGIBLE</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -14540,47 +15907,55 @@
           <t>altnews.in</t>
         </is>
       </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DPcCJWxga06/</t>
+          <t>https://www.facebook.com/watch/?v=740149025114486</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.altnews.in/yogi-adityanath-left-to-hear-criticism-of-govt-while-ravi-kishan-was-enjoying-doctored-video-viral/</t>
+          <t>https://www.altnews.in/waterlogged-kolkata-street-did-turn-red-after-eid-qurbani-alt-news-ground-report-rebuts-police-cyber-cells-denial/</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>candidates_v2.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-08-18T01:51:54.674020+00:00</t>
+          <t>2026-09-07T18:03:31.993874+00:00</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; REJECTED</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Judged NOT the misinformation source (confidence=1.00): </t>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption states 'এ দৃশ্যটা হচ্ছে কলকাতা মিউনিসিপাল কর্পোরেশনের 44 নং ওয়ার্ড (চৌরঙ্গি বিধানসভা) উত্তর কলকাতা জেলার' which is the same false claim made by Sajal Ghosh's Facebook post. The fact-checkers have debunked this claim, stating that the video actually originated in Dhaka.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>cand-thequint-0182</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>item-0021</t>
+          <t>cand-ap-altnews-1049</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -14590,107 +15965,3796 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>thequint.com</t>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reel/DRmx_YwjN7Y/</t>
+          <t>https://twitter.com/AAPka_Manojk/status/1935055153142378711</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.thequint.com/news/webqoof/ai-generated-yogi-lifting-weighting-without-his-hands-fact-check</t>
+          <t>https://www.altnews.in/media-outlets-link-visuals-of-chinese-fire-drill-from-2015-to-iranian-strikes-on-israeli-power-station/</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>candidates_v2_mass_thequint.jsonl</t>
+          <t>candidates_v3_altnews.jsonl</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-08-18T05:29:58.023010+00:00</t>
+          <t>2026-09-07T18:04:55.169170+00:00</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; ELIGIBLE</t>
-        </is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0.9999</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>UNVERIFIED</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>INDIAN YOGI MOVES 95 Kgs of weight in the gym with his mind!</t>
+          <t>Iran's hypersonic missile has directly hit Israel’s Haifa power plant, causing massive destruction.</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>llama3.2 judge (confidence=1.00): The caption text itself makes a specific false assertion about lifting '130 kgs' (not mentioned) and claims that it's done using one's 'mind', which is the exact same claim being debunked in the article.. NOT yet human/manual-reviewed.</t>
+          <t>llama3.2 (conf=1.00): The caption claims that Iran blew up an oil refinery in the port city of Haifa with a hypersonic missile which is not supported by evidence presented.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>cand-ap-altnews-1050</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://twitter.com/AhsanPti786/status/1934746168992649679</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/media-outlets-link-visuals-of-chinese-fire-drill-from-2015-to-iranian-strikes-on-israeli-power-station/</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:04:55.173327+00:00</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>#Iran's Khyber-Shark missiles destroy #Israel\'s nuclear power plant in #Haifa</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=0.99): The post claims that Iran blew up an oil refinery, which is a false statement debunked by the fact check article. The caption directly references Iranian missiles destroying Israel's nuclear power plant in Haifa, making it MISINFORMATION_SOURCE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1051</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>https://twitter.com/AuctionMirza/status/1934699500297449483</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/media-outlets-link-visuals-of-chinese-fire-drill-from-2015-to-iranian-strikes-on-israeli-power-station/</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:04:55.175855+00:00</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Iran blew up an oil refinery</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption states that 'Iran blew up an oil refinery', which directly contradicts the fact-checker's conclusion in the article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1052</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Niharik43914213/status/1935272066015465720</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/media-outlets-link-visuals-of-chinese-fire-drill-from-2015-to-iranian-strikes-on-israeli-power-station/</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:04:55.178748+00:00</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>ईरान तेल में रिफाइनरी ही उड़ा दिया शहर बर्बाद *****युद्ध करे तो मन से करे  जैसे इजराइल   उस हद तक जा रहा जहां दुश्मन पहन मागे</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1053</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>https://twitter.com/SilentlySirs/status/1934698258661519832</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/media-outlets-link-visuals-of-chinese-fire-drill-from-2015-to-iranian-strikes-on-israeli-power-station/</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:04:55.181857+00:00</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>The Bazan Oil Refinery in Haifa has been hit — with damage to pipeline systems and fires breaking out at the site.</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): This post's caption directly states that 'the' (implied) Bazan Oil Refinery in Haifa has been hit, which is a false claim debunked by the fact-check article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1055</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>https://twitter.com/mkeshari/status/1935035295537242550</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/iran-israel-conflict-old-video-of-woman-dancing-in-rain-viral-as-iranian-women-sending-message-to-islamic-regime/</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:06:01.156707+00:00</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>An Iranian woman’s powerful message to the Islamic regime: “We’ll dance on your grave with joy and hope. The murderers of Iran’s children and women will fall. Your regime will perish.• #IranRevolution #IranIsraelConflict #IranIsrael https://t.co/rv6JpjewHz</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption states a false claim that the video is from Iran and made by an Iranian woman as part of a message to the Islamic regime. The article debunks this claim stating Tamta Sabelashvili has no connection with the ongoing conflict in Iran and Israel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1056</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>https://twitter.com/realMaalouf/status/1934944645538324485</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/iran-israel-conflict-old-video-of-woman-dancing-in-rain-viral-as-iranian-women-sending-message-to-islamic-regime/</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:06:01.160288+00:00</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>The Islamic regime will perish!</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption directly states the false claim made by users like @realMaalouf, which is debunked in the fact-check article as baseless and misleading.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1062</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>https://twitter.com/RahulKaswanMP/status/1932430811233489190</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/false-claim-by-rajasthan-police-that-churu-dsp-didnt-slap-female-constable-video-is-not-edited/</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:07:30.671510+00:00</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>झूठी और बेबुनियाद FIR चूरू पुलिस द्वारा अपनी नाकामी छूपाने का प्रयास है।</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption text states the debunked claim that Churu police lodged a false FIR against Congress workers by claiming the viral video was edited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1063</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>https://twitter.com/hanumanbeniwal/status/1932085201108423133</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/false-claim-by-rajasthan-police-that-churu-dsp-didnt-slap-female-constable-video-is-not-edited/</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:07:30.675051+00:00</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>चुरू जिले में कार्यरत एक RPS अधिकारी द्वारा अपने अधीनस्थ कार्यरत महिला पुलिस कार्मिक पर हाथ उठाना निंदनीय व अशोभनीय कृत्य है तथa यह नारी शक्ति का अपमान है,एक तरफ महिला शिक्षा को बढ़ावा देने व सरकारी क्षेत्र में महिलाओं की भूमिका बढ़ाने की बातें सरकारें करती है मगर दूसरी तरह जब…</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption text of the post states a debunked claim made by Hanuman Beniwal in his tweet about DSP Sunil Jhajharia slapping a female police officer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1066</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Ayesha786Majid/status/1934568710960033987</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/viral-video-of-israeli-soldier-pleading-iran-for-mercy-is-ai-generated/</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:08:49.248091+00:00</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>इज़राइल के सैनिक ईरान से रो रो कर रहम की भीख मांग रहे हैं…!</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1069</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Skylar_Soul_/status/1934579033766838524</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/viral-video-of-israeli-soldier-pleading-iran-for-mercy-is-ai-generated/</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:08:49.257240+00:00</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>इज़राइल के सैनिक ईरान से रो रो कर रहम की भीख मांग रहे हैं...!</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption states the same claim as in the fact-check article, which has been debunked by the article itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1071</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>https://twitter.com/dpsingh1313/status/1934549976161370155</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/viral-video-of-israeli-soldier-pleading-iran-for-mercy-is-ai-generated/</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:08:50.680558+00:00</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>[इज़राइल के सैनिक ईरान से रो रो कर रहम की भीख मांग रहे हैं…!😂]</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): [The article states that Veo is an AI-based tool used to generate realistic videos without anatomical abnormalities]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1072</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>https://twitter.com/hammehaiindia62/status/1934576948442980863</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/viral-video-of-israeli-soldier-pleading-iran-for-mercy-is-ai-generated/</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:08:50.813155+00:00</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>ईरान! रुक जाओ, भगवान के लिए, हम समर्पण कर रहे हैं!</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption of the post states a claim that is directly contradicted by the fact-check article. The article clearly debunks this video as AI-generated and not real, while the poster's own text claims it shows an Israeli soldier begging for mercy from Iran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1076</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>https://twitter.com/F5xLyB7vFWa4ies/status/1933598805640815060</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/more-old-videos-of-missile-strikes-viral-as-irans-june-attack-on-israel/</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:10:04.540269+00:00</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post states that Tel Aviv was attacked with missiles in an urgent message about cities burning, which does not match any claims debunked by fact-checkers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1080</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>https://twitter.com/AlMayadeenNews/status/1841166630703030583</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/videos-of-irans-october-2024-strikes-on-israel-resurface-as-visuals-of-june-conflict/</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:11:34.835031+00:00</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>\u0631\u0644\u0627\u06cc\u0650 \u067e\u066f\u0686\u0698\u07ae\u070d\u077b\u0785\u079c\u0769</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): \u0644\u0627ی ِ \u067e\u066f\u0686\u0698\u07ae\u070d\u077b\u0785\u079c\u0769</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1082</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/carloszup/videos/1056006849521374</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/videos-of-irans-october-2024-strikes-on-israel-resurface-as-visuals-of-june-conflict/</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:11:34.841810+00:00</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>#Iran lanza un ataque con misiles hacia #Israel.</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The Facebook post's own caption/text claims that Iran launched a missile attack on Israel, which is the exact false claim debunked by the fact-check article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1084</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>https://twitter.com/thenewsbasket/status/1930944391016808742</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/in-begusarai-film-named-pakadwa-vivah-was-being-shot-video-shared-as-real-incident/</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:13:27.830918+00:00</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">बेगूसराय के एक सरकारी स्कूल टीचर को बंदूक की नोक पर पकड़वा कर शादी करवाने के लिए ले जाया जा रहा </t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states the false claim that a teacher was kidnapped for marriage at gunpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1091</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=yZ5zCEG5pCY</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/late-rajiv-dixit-imaginary-claim-about-satsada-bet-kutch-gujarat-false/</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:13:58.191466+00:00</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>गुजरात सरकार ने 60,000 वर्ग किलोमीटर का एक द्वीप अमेरिकी कंपनी को मात्र 15 पैसे प्रति वर्ग किलोमीटर की दर से बेच दिया।</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=0.90): The caption states the claim that an island was sold to Cargill for a very low price, which is debunked by the fact-check article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1092</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Jatassociation/status/1933707243536732291</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/israel-defense-forces-shared-an-old-video-as-iranian-missiles-over-israel-recently/</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:14:42.986957+00:00</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>इज़राइल गाज़ा जैसे तरह ईरान को भी इजरायल एक दम समतल कर रहा है</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=0.90): The caption states a false claim about Israel's actions towards Iran in the same vein as the original viral video that was debunked by fact-checkers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1094</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/1199454547799745</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/israel-defense-forces-shared-an-old-video-as-iranian-missiles-over-israel-recently/</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:14:42.992071+00:00</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The original text states 'Israel launched blistering attacks... claiming this was raw footage' and also mentions other users sharing similar claims with incorrect dates but the Facebook post only says TeL Aviv without any context or claim, making it a MISINFORMATION_SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1098</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>https://twitter.com/osSWSso/status/1933655365578862810</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-missile-attack-on-sevastopol-crimea-in-2024-viral-as-recent-iranian-offensive-on-jaffa-near-tel-aviv-israel/</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:17:02.082265+00:00</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>\u0639\u0627\u0644\u0650\u06cc \u0645\u0631\u0646 و\u061e\u060c\u05f3\u066a, \u0692\u068b\u067e \u0599\u0627\u0644\u0650\u06cc. -- \u0645\u0631\u0646: ޘު ࢯ׳ ࠌג, ښڋپ.</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption states the false claim that Iran is attacking Jaffa in Israel and says 'Jafaa is burning'. The article debunks this by tracing back to a video from March 24, 2024, showing Ukraine's attack on Sevastopol.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1100</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://twitter.com/RoyalIntel_/status/1933608605527187628</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-shared-in-january-2025-as-fireworks-in-berlin-now-viral-as-visuals-from-israel-iran-airstrikes/</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:17:28.254976+00:00</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>1</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>[The post's own caption/text itself makes the false claim that it is from Iran, which is debunked by the article]</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): [The post's caption is identical in wording and structure as the article debunks, which makes it a clear MISINFORMATION_SOURCE]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1110</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/middayindia/videos/593792206089749</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-from-2023-nepal-plane-crash-viral-as-last-moments-from-inside-air-india-flight-that-crashed-in-ahmedabad/</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:18:43.980069+00:00</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>#watch: A sudden fire engulfs the plane as the heart-wrenching and horrifying Facebook live video of a Nepal plane crash by one of the flyers goes viral.</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption itself states that it is 'a Facebook Live' captured on January 16, 2023. This claim directly contradicts what was stated in the fact-check article: The video shows a livestream by a flyer from 2023 and depicts moments before a Yeti Airlines flight crashed in Nepal in January 2023.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1112</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LIMRwgLYO9s</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/2022-video-of-patna-high-court-judge-reprimanding-cop-linked-to-sharmishta-panoli-case/</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:19:06.784122+00:00</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=0.80): </t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1114</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>https://twitter.com/AmitShah/status/1837027956990038451</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/2006-image-shared-as-adivasi-killed-in-chhattisgarh-and-lebelled-as-naxals/</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:20:44.008308+00:00</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>मोदी सरकार 31 मार्च 2026 से पहले देश से नक्सलवाद को पूरी तरह से समाप्त कर देगी।</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=0.90): This classification was chosen because the X Post's own Caption/Text itself makes the debunked claim stated in the Fact-Check Article Text (Amit Shah’s pledge).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1124</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>https://twitter.com/NaveedR95475805/status/1930262587310215457</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/2017-video-of-two-policemen-torturing-a-man-in-up-goes-viral-again/</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:21:55.815823+00:00</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">जो जनता पर कर रही है अत्याचार   बीजेपी सरकार में जनता पर दिन प्रतिदिन अत्याचार बढ़ता चला जा रहा है। </t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text itself makes the false claim that police under Yogi Adityanath are committing atrocities on public, which is debunked by fact-checking wing of Uttar Pradesh Police in June 5th article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0021</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>item-0034</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>https://twitter.com/foxwoundband/status/1266613385862447104</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/06/fact-check-atlanta-did-not-deploy-a-child-militia-during-protests.html</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2026-09-07T14:37:22.560671+00:00</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Atlanta has deployed a child militia at Lenox Mall fitted with riot shields and batons.</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states the debunked claim that Atlanta deployed 'a child militia' during recent protests.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0437</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=J1OvDB_wavI</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-Kamala-Harris-did-not-call-Joe-Biden-a-racist-and-a-rapist.html</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:00:01.217068+00:00</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K109" t="n">
+        <v>1</v>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): The post's caption states: 'Sen. Kamala Harris of California blasts former Vice President Joe Biden for his previously held opinions on busing in schools.' This statement is false because it misrepresents what happened during their debate, where she criticized him but did not call him a racist or use the word </t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0457</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=6BEfZCH1nN8</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-annabelle-doll-did-not-escape-from-the-warren's-occult-museum.html</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:02:23.976555+00:00</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K110" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Annabelle doll escaped from The Warrens Occult Museum today 3.00 A.M.</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The claim that Annabelle the doll 'escaped' is stated in the post's own caption, which directly contradicts the debunked information provided by Tony Spera and other sources. The original article text explicitly states: "Annabelle did not escape..." This confirms that this Instagram post contains misinformation about the event.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0460</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=LFBYZ4rwjbw</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-cdc-did-not-predict-an-outbreak-of-afm-cases-to-cover-up-anticipated-future-vaccine-injuries.html</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:03:23.631057+00:00</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K111" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0469</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>item-0049</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>https://twitter.com/livesmattershow/status/1295253759291879424</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-the-truck-driver-attacked-in-portland-near-black-lives-matter-protest-has-not-died.html</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:06:00.175987+00:00</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K112" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>The truck driver attacked in Portland has passed.</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): This post's own caption/text states the debunked claim that 'the man who was attacked on video during a protest' (has) "passed" which is false according to Lead Stories article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0503</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>https://twitter.com/DavidBrodyCBN/status/1296158619294146560</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-democrats-did-not-take-out-under-god-from-the-nightly-pledge-of-allegiance-at-their-national-convention.html</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:08:29.920219+00:00</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K113" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): [[The post's caption states the debunked claim that Democrats left out 'Under God' from their nightly Pledge of Allegiance at the Democratic National Convention, which is contradicted by fact-check article text]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0504</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>item-0050</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>https://twitter.com/DavidBrodyCBN/status/1296164465432580099</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-democrats-did-not-take-out-under-god-from-the-nightly-pledge-of-allegiance-at-their-national-convention.html</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:08:29.923565+00:00</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K114" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>"Dems recited our beautiful pledge of allegiance tonight and took out 'UNDER GOD' !"}</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The Facebook screenshot shows videos embedded with each night's program including recitation of pledge where 'under god' was included in all four nights; The post claims that "Dems took out" words, but no such claim is made about Muslim Delegates Assembly or LGBT caucuses which are mentioned separately. Hence the caption itself makes a false statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0528</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>https://twitter.com/_SJPeace_/status/1298670510360928259</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-man-protecting-his-business-in-Kenosha-did-not-own-gas-station-where-he-allegedly-fired-at-protesters.html</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:10:41.760976+00:00</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K115" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>A 17 y/o white supremacist, Kyle Rittenhouse, drove from Illinois to Wisconsin w/ an AR-15 to TERRORIZE BLM PROTESTORS He shot several people ended up killing 2. Then is able to casually walk around police as if he didn't just murder! WHAT THE FUCK?!</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post contains several false claims, including the accusation that Rittenhouse was a white supremacist and drove to Kenosha with an intention to terrorize BLM protesters using an AR-15 (the actual weapon used by Kyle Rittenhouse resembled this rifle but it's called 'AR-style' semi-automatic). The caption also includes sensational language ('TERRORIZE', 'WHITE SUPREMACIST') that is not supported by evidence. In contrast, the fact-check article debunks these claims and provides context about Rittenhouse's background.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0537</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>item-0051</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>https://twitter.com/CalebJHull/status/1298832317033705472</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/08/fact-check-cnn-did-use-the-chyron-fiery-but-mostly-peaceful-protests-after-police-shooting.html</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:11:57.416994+00:00</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K116" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0554</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>item-0052</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>https://twitter.com/TrumpWarRoom/status/1300495064838397952</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-war-room---text-trump-to-88022-on-twitter.html</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:15:01.730401+00:00</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K117" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>'You won't be safe in Joe Biden's America!'</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post itself states the exact phrase 'Joe Biden says "You won't be safe in Joe Biden's America!"' which matches exactly with what Trump campaign tweeted and misleadingly presented as a quote from Biden, making it MISINFORMATION_SOURCE.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0573</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>item-0053</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ProjectLincoln/status/1300905344693153796</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-did-not-say-americans-are-going-to-die-when-hes-not-president-in-doctored-lincoln-project-video.html</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:38:29.761925+00:00</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K118" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>going to die (when he isn't president)</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The article explicitly states that the Lincoln Project's video deceptively snipped footage from Trump's interview and took his words out of context. The actual quote is 'they're going to die' which refers to NBC ratings dying in five years when he isn't president.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0597</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=UE_3LDvWcbY</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-video-does-not-show-portland-antifa-anarchist-camps-they-are-temporary-outdoor-homeless-shelters.html</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-09-07T16:49:46.109220+00:00</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K119" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>This encampment is filled with young vibrant people who are actively, at night, committing crimes...</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): [The narrator] says 'I'm not filming General homeless individuals.' This is a clear indication that he does not want people with general homelessness issues in the camp and instead focuses on young vibrant people who are actively committing crimes at night, which was later debunked by Denis Theriault as false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0641</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=66seIj5nN9g</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-canada-has-not-criminalized-wearing-of-masks-social-distancing-and-other-covid-precautions.html</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-09-07T17:59:19.499388+00:00</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>A Law was passed today by a council of Canadian citizens’ assemblies that struck down and criminalized all COVID measures requiring masking, distancing, quarantining, and vaccines.</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">llama3.2 (conf=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0642</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=dq_IXYBYu1o</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-canada-has-not-criminalized-wearing-of-masks-social-distancing-and-other-covid-precautions.html</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-09-07T17:59:19.501854+00:00</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K121" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>'CRIMINAL' all Covid19 forceful measures requiring its people to wear masks, social distance, quarantine, or Vaccinate!!!</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): [The post's caption states the debunked claim that Canada criminalized government measures such as mask-wearing and vaccinations. The article clearly debunks this claim by stating there is no national declaration made on September 8, 2020, regarding these measures.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0669</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://twitter.com/josie_huang/status/1305102941624229889</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-protesters-did-not-block-hospital-entrance-before-arrival-of-ambulances-transporting-wounded-officers.html</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:02:18.970586+00:00</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K122" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>protesters blocking the entrance to hospital before ambulances arrived.</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states that protesters were stopped by police and security 'before they got to the entrance' of the hospital. This directly contradicts the claim made in the Facebook page "Officer Parker" post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0686</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://twitter.com/KarluskaP/status/1305929080634777600</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-joe-biden-was-not-waving-to-an-empty-field-firefighters-in-background.html</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:04:44.482451+00:00</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K123" t="n">
+        <v>1</v>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>he’s waving to a empty field!</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states the debunked claim that Joe Biden waved at an 'empty' field, which is not true according to the fact-check article. The use of all caps and exaggerated emojis (🤣) in the caption emphasizes this false narrative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0688</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=QhCg_q5IjjY</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-joe-biden-was-not-waving-to-an-empty-field-firefighters-in-background.html</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:04:44.490476+00:00</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K124" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>he was waving to an empty field!</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states the debunked claim that Joe Biden waved to no one in a full video context.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0710</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=lMUba-CvN_s</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-cnn-did-not-demand-kayleigh-mcenany-resign.html</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:07:37.148783+00:00</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K125" t="n">
+        <v>0.9999</v>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>CNN has now joined the chorus in [calling] for Kayleigh McEnany to resign.</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption of the YouTube video posted by Lets be Frank contains the exact phrase 'CNN has now joined the chorus in [calling] for Kayleigh McEnany to resign.' This is a direct quote from Lockhart's opinion piece, which was written as an independent commentary and not reflective of CNN's views. The Editor's Note at the bottom of the article clearly states that it is Lockhart's 'opinion' and not CNN's view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0713</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/watch/?v=1949373388675200</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-kohls-does-sell-blue-lives-matter-apparel.html</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:08:27.217332+00:00</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K126" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): This Facebook post contains a statement from 'Thin Blue Line USA Official Statement' that explicitly rejects any association of their flag with racism and hatred. This contradicts the claim made in this caption which implies Kohl's only sells Black Lives Matter merchandise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0724</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=e4PaZHHOC2M</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-blm-antifa-instigators-not-charged-arrested-for-california-oregon-wildfires-arson.html</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:09:18.351848+00:00</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K127" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>at least one of the arsonists charged and arrested was also an instigator in BLM rallies.</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption states that at least ONE of the arsonists charged and arrested was 'also' an instigator in BLM rallies. However, according to the fact-check article, only Jeffrey Acord has a connection to Black Lives Matter protests or Antifa rioting, but even then, his involvement is not with starting wildfires. The post's claim that at least one of these arsonists were also involved in BLM rallies is false.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0727</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/watch/?v=10157859721016880</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-bill-gates-does-not-have-a-doctorate-in-immunology-virology-and-toxicology.html</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:10:01.309441+00:00</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K128" t="n">
+        <v>1</v>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>BILL GATES HAS A DOCTORATE IN IMMUNOLOGY, VIROLOGY AND TOXICOLOGY</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption explicitly states the false claim without any qualification or context that would suggest it's being presented as an opinion or speculation. The language used is straightforward and factual-sounding, which makes this classification clear-cut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0747</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://twitter.com/SteveGuest/status/1308134517081886720</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-joe-biden-did-not-botch-the-pledge-of-allegiance.html</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:13:16.862612+00:00</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K129" t="n">
+        <v>1</v>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Joe Biden completely botches the Pledge of Allegiance</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption states that Joe Biden 'completely botched' the pledge during a campaign speech, which is not true and was taken out of context as stated in the fact-check article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0749</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>instagram</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/CFcQBNUgtYe/</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-joe-biden-did-not-botch-the-pledge-of-allegiance.html</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:13:16.869394+00:00</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K130" t="n">
+        <v>1</v>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>[Joe Biden] completely botches the Pledge of Allegiance</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The Instagram post's caption states that Joe Biden 'completely botched' the Pledge of Allegiance during a campaign speech, which is false according to the fact-check article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0752</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://twitter.com/BraddJaffy/status/789866170539208708</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-has-not-been-accused-in-court-of-sexually-assaulting-26-females-including-seven-minors.html</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:13:47.478197+00:00</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K131" t="n">
+        <v>1</v>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Yes, that's not true. While some reports have indeed put the number of allegations against Trump at 26 since the 1970s...</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's caption states a debunked claim made by President Trump himself. The article debunks this claim stating that not all 26 reports were filed in court and only one alleges child abuse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0755</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=nLbubCJHm94</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-trump-has-not-been-accused-in-court-of-sexually-assaulting-26-females-including-seven-minors.html</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:13:47.488837+00:00</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K132" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>TWENTY-SIX SEXUAL ASSAULT ALLEGATIONS filed in court?? and SEVEN are against CHILDREN</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=0.90): The Instagram post's own caption/text states that Trump has TWENTY-SIX sexual assault allegations filed in court, including seven against children. However, according to the fact-check article, not all of these reports have been filed in court and there is only one claim that accuses Trump of abusing a child.
+Additionally, the tweet from which this post was archived also states 'SEVEN are against CHILDREN', but as mentioned earlier, it's just ONE such case. The caption itself contains false information about the number of allegations.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0758</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://twitter.com/TelemundoNews/status/1308829204264484873</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-joe-biden-did-not-use-a-teleprompter-to-answer-questions-during-an-interview-with-telemundo.html</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:14:22.614068+00:00</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K133" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>he has to use a teleprompter for a 1 on 1 interview!!!</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=0.90): The post's caption directly states the false claim that Joe Biden used a teleprompter during an interview with Telemundo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0810</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=OBuCCydVpxA</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/09/fact-check-joe-biden-iv-up-his-sleeve.html</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:19:13.219091+00:00</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K134" t="n">
+        <v>1</v>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>caught wearing a mic and earpiece</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The caption claims that Joe Biden was caught wearing a 'mic' (presumably an audio device) during the debate, which is not true according to the fact-check article.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0827</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://twitter.com/realDonaldTrump/status/1311493853615071232</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/10/fact-check-the-united-states-has-not-labeled-antifa-a-terrorist-group.html</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:21:05.277419+00:00</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K135" t="n">
+        <v>1</v>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Antifa is a domestic terrorist organization.</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): The post's own caption/text states the claim that antifa has been labeled as a 'domestic terrorist organisation' by President Trump and others. However, according to the fact-check article provided, no formal designation listing antifa as a terrorist organization was made.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>cand-ap-leadstories-0844</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>leadstories.com</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>youtube</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=rzX31JCPGuI</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://leadstories.com/hoax-alert/2020/10/fact-check-the-simpsons-tv-show-did-not-air-a-scene-with-donald-trump-in-a-coffin.html</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>candidates_v3_leadstories.jsonl</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:22:18.352479+00:00</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="K136" t="n">
+        <v>1</v>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Es sorprendente la manera en que una simple serie animada de monos amarillos, nos ha dejado con la boca abierta al hacer predicciones... Hechos como la caída de las torres gemelas, la aparición del ébola y el triunfo de Donald Trump como el nuevo presidente de Estados Unidos...</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>llama3.2 (conf=1.00): [The caption claims that The Simpsons predicted the fall of the Twin Towers and the election of Donald Trump as US President], which is a false claim debunked by Snopes in February 2017.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>cand-mass-0027</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>item-0019</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DX7LBwesE-o/</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/bjp-media-outlets-share-holi-video-as-people-celebrating-bjp-victory-in-bengal/</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>candidates_v2.jsonl</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-08-18T00:59:01.077843+00:00</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; GROUND_TRUTH_VERIFIED -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>False claim: The post's own caption asserts that it depicts people celebrating a political event (BJP victory), but actually shows a pre-election celebration during Holi.</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Celebrations of Jai Sri Ram at the Holi celebrations in Kolkata, which took place two months before May 4th</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>llama3.2 judge (confidence=0.90): The Instagram Post’s Own Caption Asserts the False Claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>cand-mass-0088</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DPcCJWxga06/</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/yogi-adityanath-left-to-hear-criticism-of-govt-while-ravi-kishan-was-enjoying-doctored-video-viral/</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>candidates_v2.jsonl</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-08-18T01:51:54.674020+00:00</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; ARTICLE_FOUND -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; REJECTED</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Judged NOT the misinformation source (confidence=1.00): </t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>cand-thequint-0182</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>item-0021</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>thequint.com</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DRmx_YwjN7Y/</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.thequint.com/news/webqoof/ai-generated-yogi-lifting-weighting-without-his-hands-fact-check</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>candidates_v2_mass_thequint.jsonl</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-08-18T05:29:58.023010+00:00</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>INDIAN YOGI MOVES 95 Kgs of weight in the gym with his mind!</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>llama3.2 judge (confidence=1.00): The caption text itself makes a specific false assertion about lifting '130 kgs' (not mentioned) and claims that it's done using one's 'mind', which is the exact same claim being debunked in the article.. NOT yet human/manual-reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>cand-vishvas-1173</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B140" t="inlineStr">
         <is>
           <t>item-0022</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D140" t="inlineStr">
         <is>
           <t>vishvasnews.com</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F140" t="inlineStr">
         <is>
           <t>https://www.instagram.com/reel/C3tynQjr_wI/</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G140" t="inlineStr">
         <is>
           <t>https://www.vishvasnews.com/politics/fact-check-akhilesh-yadav-old-video-from-kanpur-is-being-shared-as-meeting-farmers-in-delhi/</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>candidates_v2_mass_vishvas.jsonl</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I140" t="inlineStr">
         <is>
           <t>2026-08-18T10:12:40.325601+00:00</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J140" t="inlineStr">
         <is>
           <t>DISCOVERED -&gt; SOCIAL_REFERENCE_FOUND -&gt; MEDIA_RETRIEVABLE -&gt; ELIGIBLE -&gt; UNRESOLVED -&gt; ELIGIBLE</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr">
+      <c r="L140" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr">
+      <c r="M140" t="inlineStr">
         <is>
           <t>अखिलेश यादव किसानों से मिलने दिल्ली पहुंचे।</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
+      <c r="N140" t="inlineStr">
         <is>
           <t>llama3.2 judge (confidence=1.00): The caption text itself makes the specific false assertion that 'अखिलेश यादव' is meeting with farmers in Delhi, which contradicts the fact-check article's conclusion.. NOT yet human/manual-reviewed.</t>
         </is>
@@ -14734,7 +19798,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07T17:17:45+00:00</t>
+          <t>2026-09-07T18:34:47+00:00</t>
         </is>
       </c>
     </row>
@@ -14745,7 +19809,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -14765,7 +19829,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -14807,7 +19871,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -14817,7 +19881,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
@@ -14827,7 +19891,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -14845,7 +19909,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -14875,7 +19939,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -14893,7 +19957,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20">
@@ -14903,7 +19967,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -14931,7 +19995,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24">
@@ -14959,7 +20023,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27">
@@ -14987,7 +20051,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30">
@@ -14997,33 +20061,33 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">    misleading_context</t>
+          <t xml:space="preserve">    quote</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    visual</t>
+          <t xml:space="preserve">    misleading_context</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    quote</t>
+          <t xml:space="preserve">    visual</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -15045,7 +20109,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -15073,33 +20137,33 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    boomlive.in</t>
+          <t xml:space="preserve">    leadstories.com</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:boomlive.in</t>
+          <t xml:space="preserve">    boomlive.in</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:altnews.in</t>
+          <t xml:space="preserve">    tier-1-source:boomlive.in</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -15109,17 +20173,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:factly.in</t>
+          <t xml:space="preserve">    tier-1-source:altnews.in</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:boomlive.in (hindi.boomlive.in)</t>
+          <t xml:space="preserve">    tier-1-source:factly.in</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -15129,7 +20193,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:altnews.in (hindi.altnews.in)</t>
+          <t xml:space="preserve">    tier-1-source:boomlive.in (hindi.boomlive.in)</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -15139,7 +20203,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    thequint.com</t>
+          <t xml:space="preserve">    tier-1-source:altnews.in (hindi.altnews.in)</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -15149,7 +20213,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    vishvasnews.com</t>
+          <t xml:space="preserve">    thequint.com</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -15159,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    leadstories.com</t>
+          <t xml:space="preserve">    vishvasnews.com</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -15181,7 +20245,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50">
@@ -15209,7 +20273,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53">
@@ -15237,7 +20301,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
@@ -15275,7 +20339,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="60">
@@ -15285,7 +20349,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -15295,7 +20359,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
@@ -15305,7 +20369,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63">
@@ -15323,7 +20387,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65">
@@ -15352,7 +20416,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0/47 (0%)</t>
+          <t>0/56 (0%)</t>
         </is>
       </c>
     </row>
@@ -15364,7 +20428,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>38/47 (80%)</t>
+          <t>47/56 (83%)</t>
         </is>
       </c>
     </row>
@@ -15376,7 +20440,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9/47 (19%)</t>
+          <t>9/56 (16%)</t>
         </is>
       </c>
     </row>
@@ -15388,7 +20452,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>9/47 (19%)</t>
+          <t>9/56 (16%)</t>
         </is>
       </c>
     </row>
@@ -15400,7 +20464,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>47/47 (100%)</t>
+          <t>56/56 (100%)</t>
         </is>
       </c>
     </row>
@@ -15412,7 +20476,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>9/47 (19%)</t>
+          <t>9/56 (16%)</t>
         </is>
       </c>
     </row>

--- a/research/dataset/TruthLens_Dataset.xlsx
+++ b/research/dataset/TruthLens_Dataset.xlsx
@@ -469,7 +469,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-07T18:54:07+00:00</t>
+          <t>2026-09-07T19:30:06+00:00</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6cc317e</t>
+          <t>f6f8b5b</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK66"/>
+  <dimension ref="A1:AK76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -8381,6 +8381,1216 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>item-0070</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D67" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1038</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://twitter.com/realMaalouf/status/1935182415124660459</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-iranian-women-protesting-mahsa-aminis-custodial-killing-in-2022-linked-to-june-conflict-with-israel/</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>A video of Iranian female students removing their headscarves and chanting against the regime shows fresh unrest inside Iran during the June 2025 Iran-Israel conflict.</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>Alt News: the footage is from 2022 protests over Mahsa Amini's custodial killing, not the June 2025 conflict (article title: 'Video of Iranian women protesting Mahsa Amini's custodial killing in 2022 linked to June conflict with Israel').</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-of-iranian-women-protesting-mahsa-aminis-custodial-killing-in-2022-linked-to-june-conflict-with-israel/</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W67" t="b">
+        <v>1</v>
+      </c>
+      <c r="X67" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>762b38243e9fd0a8b940f31580cf2abeb305d19f6883f8291c642084f01f83f1</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-08</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:02:26.691128+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>item-0071</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D68" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1042</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sajalghoshofc/videos/1255513172727328</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/waterlogged-kolkata-street-did-turn-red-after-eid-qurbani-alt-news-ground-report-rebuts-police-cyber-cells-denial/</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>bn</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>BJP</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>A viral video showing a blood-red waterlogged street in the Bowbazar area of central Kolkata after Bakri Eid's Qurbani ritual is genuine and from that location.</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>Alt News's own ground report confirmed the street did turn red with blood-tinged rainwater after the Qurbani and rebutted the Kolkata Police cyber cell's claim that the video was edited/fake (article title: 'Waterlogged Kolkata street did turn red after Eid Qurbani -- Alt News ground report rebuts police cyber cell's denial').</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/waterlogged-kolkata-street-did-turn-red-after-eid-qurbani-alt-news-ground-report-rebuts-police-cyber-cells-denial/</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W68" t="b">
+        <v>0</v>
+      </c>
+      <c r="X68" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z68" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD68" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>d5af54d37374429ac3b5b90e07d2b6a31d4ec1376dcd4628ef2d0f22fb9fa082</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-08</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:03:29.881226+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>item-0072</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D69" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1053</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://twitter.com/SilentlySirs/status/1934698258661519832</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/media-outlets-link-visuals-of-chinese-fire-drill-from-2015-to-iranian-strikes-on-israeli-power-station/</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>A video of a huge explosion at a power plant shows Iranian missiles destroying the Bazan Oil Refinery in Haifa, Israel during the June 2025 Iran-Israel conflict.</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Alt News: the video is of a Chinese fire drill from 2015, unrelated to the conflict (article title: 'Media outlets link visuals of Chinese fire drill from 2015 to Iranian strikes on Israeli power station').</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/media-outlets-link-visuals-of-chinese-fire-drill-from-2015-to-iranian-strikes-on-israeli-power-station/</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W69" t="b">
+        <v>1</v>
+      </c>
+      <c r="X69" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD69" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>89e769bb054511fcf535c9a0adc7f7b4c96708d8c97e2d046d764e68ca572b7b</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-08</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:04:55.181857+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>item-0073</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1056</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>https://twitter.com/realMaalouf/status/1934944645538324485</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/iran-israel-conflict-old-video-of-woman-dancing-in-rain-viral-as-iranian-women-sending-message-to-islamic-regime/</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>A video of a woman dancing in the rain shows Iranian women defying the Islamic regime's restrictions on women during the June 2025 Iran-Israel conflict.</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Alt News: the ~12-second clip is an old video with no connection to Iran or to the June 2025 conflict (article title: 'Iran-Israel conflict: old video of woman dancing in rain viral as Iranian women sending message to Islamic regime').</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/iran-israel-conflict-old-video-of-woman-dancing-in-rain-viral-as-iranian-women-sending-message-to-islamic-regime/</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W70" t="b">
+        <v>1</v>
+      </c>
+      <c r="X70" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z70" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD70" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>67598f0c738b980c34643c988e65d935f82a31a9fa15da6d1a7436210756ee0a</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-08</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:06:01.160288+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>item-0074</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1063</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>https://twitter.com/hanumanbeniwal/status/1932085201108423133</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/false-claim-by-rajasthan-police-that-churu-dsp-didnt-slap-female-constable-video-is-not-edited/</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Rajasthan Police</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>A video from a Congress rally in Churu, Rajasthan authentically shows DSP Sunil Jhajharia slapping a female police constable hard on the back, and the clip is not edited.</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Alt News: the video is not edited; the Rajasthan Police's claim that the clip was doctored is false (article title: 'False claim by Rajasthan Police that Churu DSP didn't slap female constable, video is not edited').</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/false-claim-by-rajasthan-police-that-churu-dsp-didnt-slap-female-constable-video-is-not-edited/</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W71" t="b">
+        <v>1</v>
+      </c>
+      <c r="X71" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD71" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>a0d56bbc873d5a6e7aaf92d92140002689168c81acefb018ebde2f7aba9d4564</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-08</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:07:30.675051+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>item-0075</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1069</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>https://twitter.com/Skylar_Soul_/status/1934579033766838524</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/viral-video-of-israeli-soldier-pleading-iran-for-mercy-is-ai-generated/</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>A video shows a real Israeli soldier tearfully begging the Iranian army to stop its attacks, saying 'Half of Israel is gone. We surrender. Just stop this destruction,' during the June 2025 Iran-Israel conflict.</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>Alt News: the video is AI-generated (article title: 'Viral video of Israeli soldier pleading Iran for mercy is AI-generated').</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/viral-video-of-israeli-soldier-pleading-iran-for-mercy-is-ai-generated/</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W72" t="b">
+        <v>1</v>
+      </c>
+      <c r="X72" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD72" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>b65b32433c7c768099fa205e50be6dddf139c0b22ab785e3d52fd13b1534dcd0</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-08</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:08:49.257240+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>item-0076</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D73" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1076</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>https://twitter.com/F5xLyB7vFWa4ies/status/1933598805640815060</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/more-old-videos-of-missile-strikes-viral-as-irans-june-attack-on-israel/</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>A 46-second video compilation shows Iran's retaliatory missile attacks striking Tel Aviv on June 14, 2025.</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Alt News: the compilation is made of three separate old / unrelated missile-strike videos, not footage of the June 14 attack (article title: 'More old videos of missile strikes viral as Iran's June attack on Israel').</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/more-old-videos-of-missile-strikes-viral-as-irans-june-attack-on-israel/</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W73" t="b">
+        <v>1</v>
+      </c>
+      <c r="X73" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y73" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD73" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>8e1fe993976659c883112e074547c501f4011866c7bf086a73c4b7947eb317b7</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-08</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:10:04.540269+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>item-0077</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D74" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1084</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>https://twitter.com/thenewsbasket/status/1930944391016808742</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/in-begusarai-film-named-pakadwa-vivah-was-being-shot-video-shared-as-real-incident/</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>A video shows armed men dragging a government school teacher out of a school in Begusarai, Bihar to force him into marriage ('Pakadwa Vivah') at gunpoint.</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>Alt News: the footage is from the shooting of a film titled 'Pakadwa Vivah', not a real incident (article title: 'In Begusarai, film named Pakadwa Vivah was being shot, video shared as real incident').</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/in-begusarai-film-named-pakadwa-vivah-was-being-shot-video-shared-as-real-incident/</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W74" t="b">
+        <v>1</v>
+      </c>
+      <c r="X74" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD74" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>599d1ae885d61f48e35a239f96f5ae0b13e950c4356e28c305f4efdb44d78d67</t>
+        </is>
+      </c>
+      <c r="AG74" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-08</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:13:27.830918+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>item-0078</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1094</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>facebook</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/reel/1199454547799745</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/israel-defense-forces-shared-an-old-video-as-iranian-missiles-over-israel-recently/</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>A video of an airstrike shows Iranian missiles being fired over Israel during the June 2025 Iran-Israel conflict.</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>Alt News: the video is old and unrelated to the June 2025 conflict (article title: 'Israel Defense Forces shared an old video as Iranian missiles over Israel recently').</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/israel-defense-forces-shared-an-old-video-as-iranian-missiles-over-israel-recently/</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W75" t="b">
+        <v>1</v>
+      </c>
+      <c r="X75" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD75" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>7ef9e55f9e6d23310291f805a73a70e24284ada22603b16421e32082e3723d42</t>
+        </is>
+      </c>
+      <c r="AG75" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-08</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:14:42.992071+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>item-0079</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>validation</t>
+        </is>
+      </c>
+      <c r="D76" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>cand-ap-altnews-1100</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>https://twitter.com/RoyalIntel_/status/1933608605527187628</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-shared-in-january-2025-as-fireworks-in-berlin-now-viral-as-visuals-from-israel-iran-airstrikes/</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>video</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>A seven-second clip of an explosion near a building shows Iran's missile strikes on Israel ('up close and personal from Iran') during the June 2025 conflict.</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>altnews.in</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Alt News: the same clip was shared in January 2025 as New Year fireworks in Berlin (article title: 'Video shared in January 2025 as fireworks in Berlin now viral as visuals from Israel-Iran airstrikes').</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>https://www.altnews.in/video-shared-in-january-2025-as-fireworks-in-berlin-now-viral-as-visuals-from-israel-iran-airstrikes/</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="W76" t="b">
+        <v>0</v>
+      </c>
+      <c r="X76" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z76" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>d45a30150590dd557bbd897ac7a3e9f22af6db6d15f70598a63cae49329a7e9f</t>
+        </is>
+      </c>
+      <c r="AG76" t="inlineStr">
+        <is>
+          <t>reviewed</t>
+        </is>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>claude-review-2026-09-08</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>candidates_v3_altnews.jsonl</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>2026-09-07T18:17:28.254976+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8392,7 +9602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P96"/>
+  <dimension ref="A1:P106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11919,6 +13129,276 @@
         </is>
       </c>
       <c r="F96" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>item-0070</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>A video of Iranian female students removing their headscarves and chanting against the regime shows fresh unrest inside Iran during the June 2025 Iran-Israel conflict.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>item-0071</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>A viral video showing a blood-red waterlogged street in the Bowbazar area of central Kolkata after Bakri Eid's Qurbani ritual is genuine and from that location.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>item-0072</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>A video of a huge explosion at a power plant shows Iranian missiles destroying the Bazan Oil Refinery in Haifa, Israel during the June 2025 Iran-Israel conflict.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>item-0073</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>A video of a woman dancing in the rain shows Iranian women defying the Islamic regime's restrictions on women during the June 2025 Iran-Israel conflict.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>item-0074</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>A video from a Congress rally in Churu, Rajasthan authentically shows DSP Sunil Jhajharia slapping a female police constable hard on the back, and the clip is not edited.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>item-0075</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>A video shows a real Israeli soldier tearfully begging the Iranian army to stop its attacks, saying 'Half of Israel is gone. We surrender. Just stop this destruction,' during the June 2025 Iran-Israel conflict.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>item-0076</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>A 46-second video compilation shows Iran's retaliatory missile attacks striking Tel Aviv on June 14, 2025.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>item-0077</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>A video shows armed men dragging a government school teacher out of a school in Begusarai, Bihar to force him into marriage ('Pakadwa Vivah') at gunpoint.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>item-0078</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>A video of an airstrike shows Iranian missiles being fired over Israel during the June 2025 Iran-Israel conflict.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>MISLEADING</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>item-0079</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>dataset_ground_truth</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>A seven-second clip of an explosion near a building shows Iran's missile strikes on Israel ('up close and personal from Iran') during the June 2025 conflict.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>provenance</t>
         </is>
@@ -17387,6 +18867,11 @@
           <t>cand-ap-altnews-1038</t>
         </is>
       </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>item-0070</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -17452,6 +18937,11 @@
           <t>cand-ap-altnews-1042</t>
         </is>
       </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>item-0071</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -17968,6 +19458,11 @@
           <t>cand-ap-altnews-1053</t>
         </is>
       </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>item-0072</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -18098,6 +19593,11 @@
           <t>cand-ap-altnews-1056</t>
         </is>
       </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>item-0073</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -18228,6 +19728,11 @@
           <t>cand-ap-altnews-1063</t>
         </is>
       </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>item-0074</t>
+        </is>
+      </c>
       <c r="C96" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -18358,6 +19863,11 @@
           <t>cand-ap-altnews-1069</t>
         </is>
       </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>item-0075</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -18553,6 +20063,11 @@
           <t>cand-ap-altnews-1076</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>item-0076</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -18744,6 +20259,11 @@
           <t>cand-ap-altnews-1084</t>
         </is>
       </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>item-0077</t>
+        </is>
+      </c>
       <c r="C104" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -18939,6 +20459,11 @@
           <t>cand-ap-altnews-1094</t>
         </is>
       </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>item-0078</t>
+        </is>
+      </c>
       <c r="C107" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
@@ -19063,6 +20588,11 @@
       <c r="A109" t="inlineStr">
         <is>
           <t>cand-ap-altnews-1100</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>item-0079</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -21731,7 +23261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B72"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -21758,7 +23288,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07T18:54:07+00:00</t>
+          <t>2026-09-07T19:30:06+00:00</t>
         </is>
       </c>
     </row>
@@ -21769,7 +23299,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4">
@@ -21789,7 +23319,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -21831,7 +23361,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -21841,7 +23371,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -21851,7 +23381,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -21869,7 +23399,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -21899,7 +23429,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -21917,7 +23447,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -21927,7 +23457,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -21943,197 +23473,197 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- split distribution ---</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t xml:space="preserve">    bn</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">    validation</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>56</v>
-      </c>
+          <t>--- split distribution ---</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
+          <t xml:space="preserve">    validation</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- benchmark_version distribution ---</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t xml:space="preserve">    (none)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">    v2</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>56</v>
-      </c>
+          <t>--- benchmark_version distribution ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">    v1</t>
+          <t xml:space="preserve">    v2</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>--- claim_type distribution ---</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t xml:space="preserve">    v1</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">    provenance</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>49</v>
-      </c>
+          <t>--- claim_type distribution ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">    event</t>
+          <t xml:space="preserve">    provenance</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">    quote</t>
+          <t xml:space="preserve">    event</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">    misleading_context</t>
+          <t xml:space="preserve">    quote</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">    visual</t>
+          <t xml:space="preserve">    misleading_context</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>--- media (video/photo) distribution ---</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t xml:space="preserve">    visual</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">    video</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>62</v>
-      </c>
+          <t>--- media (video/photo) distribution ---</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">    photo</t>
+          <t xml:space="preserve">    video</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>--- factchecker distribution ---</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t xml:space="preserve">    photo</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">    altnews.in</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>41</v>
-      </c>
+          <t>--- factchecker distribution ---</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">    leadstories.com</t>
+          <t xml:space="preserve">    altnews.in</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">    boomlive.in</t>
+          <t xml:space="preserve">    leadstories.com</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:boomlive.in</t>
+          <t xml:space="preserve">    boomlive.in</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:altnews.in</t>
+          <t xml:space="preserve">    tier-1-source:boomlive.in</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -22143,17 +23673,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:factly.in</t>
+          <t xml:space="preserve">    tier-1-source:altnews.in</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:boomlive.in (hindi.boomlive.in)</t>
+          <t xml:space="preserve">    tier-1-source:factly.in</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -22163,7 +23693,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier-1-source:altnews.in (hindi.altnews.in)</t>
+          <t xml:space="preserve">    tier-1-source:boomlive.in (hindi.boomlive.in)</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -22173,7 +23703,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">    thequint.com</t>
+          <t xml:space="preserve">    tier-1-source:altnews.in (hindi.altnews.in)</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -22183,7 +23713,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">    vishvasnews.com</t>
+          <t xml:space="preserve">    thequint.com</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -22193,91 +23723,91 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>--- ground-truth tier distribution ---</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t xml:space="preserve">    vishvasnews.com</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>56</v>
-      </c>
+          <t>--- ground-truth tier distribution ---</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">    1</t>
+          <t xml:space="preserve">    (none)</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>--- difficulty distribution ---</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t xml:space="preserve">    1</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>65</v>
-      </c>
+          <t>--- difficulty distribution ---</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>--- annotation_status distribution ---</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t xml:space="preserve">    (none)</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">    reviewed</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>28</v>
-      </c>
+          <t>--- annotation_status distribution ---</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (none)</t>
+          <t xml:space="preserve">    reviewed</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">    tier1_professional</t>
+          <t xml:space="preserve">    (none)</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">    needs_review</t>
+          <t xml:space="preserve">    tier1_professional</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -22287,156 +23817,166 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>--- modality availability (true count) ---</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t xml:space="preserve">    needs_review</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">    audio_available</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>50</v>
-      </c>
+          <t>--- modality availability (true count) ---</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">    ocr_available</t>
+          <t xml:space="preserve">    audio_available</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">    caption_available</t>
+          <t xml:space="preserve">    ocr_available</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">    visual_information_available</t>
+          <t xml:space="preserve">    caption_available</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>--- cross-post ---</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
+          <t xml:space="preserve">    visual_information_available</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">    cross_post_possible = true</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>56</v>
-      </c>
+          <t>--- cross-post ---</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">    cross_post_verified = true</t>
+          <t xml:space="preserve">    cross_post_possible = true</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>--- missing-field rates ---</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr"/>
+          <t xml:space="preserve">    cross_post_verified = true</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no factcheck_url</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>0/65 (0%)</t>
-        </is>
-      </c>
+          <t>--- missing-field rates ---</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no publication_date</t>
+          <t xml:space="preserve">    no factcheck_url</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>56/65 (86%)</t>
+          <t>0/75 (0%)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no media_hash</t>
+          <t xml:space="preserve">    no publication_date</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9/65 (13%)</t>
+          <t>66/75 (88%)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no split</t>
+          <t xml:space="preserve">    no media_hash</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>9/65 (13%)</t>
+          <t>9/75 (12%)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">    no difficulty</t>
+          <t xml:space="preserve">    no split</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>65/65 (100%)</t>
+          <t>9/75 (12%)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t xml:space="preserve">    no difficulty</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>75/75 (100%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t xml:space="preserve">    no candidate_id (provenance)</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>9/65 (13%)</t>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>9/75 (12%)</t>
         </is>
       </c>
     </row>
@@ -24580,7 +26120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -24633,12 +26173,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6cc317e</t>
+          <t>f6f8b5b</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Review-gated promotion batches 3-4: BENCHMARK 47 -&gt; ~66 (human-reviewed)</t>
+          <t>Review-gated batches 5-6: BENCHMARK 65 -&gt; ~84 (Iran-Israel conflict wave + US 2020)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -24646,17 +26186,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>a97658e</t>
+          <t>d20b8e6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Review-gated promotion batches 1-2: +10 human-reviewed items (BENCHMARK 42-&gt;47)</t>
+          <t>Dataset checkpoint after review batch 4 (BENCHMARK 65)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -24664,17 +26204,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>69c0ca1</t>
+          <t>6cc317e</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Checkpoint before switching to review-gated promotion (BENCHMARK=37)</t>
+          <t>Review-gated promotion batches 3-4: BENCHMARK 47 -&gt; ~66 (human-reviewed)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -24687,12 +26227,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6b2ed7b</t>
+          <t>a97658e</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dataset checkpoint: 34 benchmark items (was 22); +12 promoted from all-platform sourcing this session</t>
+          <t>Review-gated promotion batches 1-2: +10 human-reviewed items (BENCHMARK 42-&gt;47)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -24700,17 +26240,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61a7ad6</t>
+          <t>69c0ca1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Promote item-0022; fix malformed labels on 2 already-promoted items</t>
+          <t>Checkpoint before switching to review-gated promotion (BENCHMARK=37)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -24718,17 +26258,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>764c446</t>
+          <t>6b2ed7b</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Promote item-0021 from WebQoof; harden spot-check + merge locking</t>
+          <t>Dataset checkpoint: 34 benchmark items (was 22); +12 promoted from all-platform sourcing this session</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -24741,12 +26281,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>a67aad9</t>
+          <t>61a7ad6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fix real concurrent-write data loss that crashed the Alt News pipeline</t>
+          <t>Promote item-0022; fix malformed labels on 2 already-promoted items</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -24759,12 +26299,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>cdfde33</t>
+          <t>764c446</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Promote item-0018: AI-generated protest-death fabrication (benchmark: 17 -&gt; 18)</t>
+          <t>Promote item-0021 from WebQoof; harden spot-check + merge locking</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -24777,12 +26317,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>b1c577c</t>
+          <t>a67aad9</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Promote item-0017: second AI-generated-image case (benchmark: 16 -&gt; 17)</t>
+          <t>Fix real concurrent-write data loss that crashed the Alt News pipeline</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -24795,12 +26335,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1bc264e</t>
+          <t>cdfde33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fix embed-widget sourcing gap, promote item-0016 (benchmark: 15 -&gt; 16)</t>
+          <t>Promote item-0018: AI-generated protest-death fabrication (benchmark: 17 -&gt; 18)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -24808,17 +26348,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6773a7f</t>
+          <t>b1c577c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Promote all 6 ELIGIBLE v2 candidates via real ingestion (items 0010-0015)</t>
+          <t>Promote item-0017: second AI-generated-image case (benchmark: 16 -&gt; 17)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -24826,17 +26366,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>9d0a591</t>
+          <t>1bc264e</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dataset pass 3: 2 more Tier-1 items, first quote-type claim, real misses logged</t>
+          <t>Fix embed-widget sourcing gap, promote item-0016 (benchmark: 15 -&gt; 16)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -24844,17 +26384,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1767254</t>
+          <t>6773a7f</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Day 2 pass 2: 2 more Tier-1 items, closing claim-type and language gaps</t>
+          <t>Promote all 6 ELIGIBLE v2 candidates via real ingestion (items 0010-0015)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -24867,15 +26407,51 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>9d0a591</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Dataset pass 3: 2 more Tier-1 items, first quote-type claim, real misses logged</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1767254</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Day 2 pass 2: 2 more Tier-1 items, closing claim-type and language gaps</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>fbacfb9</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Day 2: held-out dataset now at 5 real Tier-1 items (up from 2), plus annotation protocol</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
